--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-1</v>
+        <v>18003</v>
       </c>
       <c r="BG4" t="n">
         <v>2</v>
@@ -2992,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-1</v>
+        <v>23546</v>
       </c>
       <c r="BG5" t="n">
         <v>2</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-1</v>
+        <v>24453</v>
       </c>
       <c r="BG6" t="n">
         <v>2</v>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-1</v>
+        <v>20254</v>
       </c>
       <c r="BG7" t="n">
         <v>2</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-1</v>
+        <v>20738</v>
       </c>
       <c r="BG8" t="n">
         <v>2</v>
@@ -4824,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-1</v>
+        <v>25044</v>
       </c>
       <c r="BG9" t="n">
         <v>2</v>
@@ -5288,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-1</v>
+        <v>11004</v>
       </c>
       <c r="BG10" t="n">
         <v>2</v>
@@ -5752,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-1</v>
+        <v>75673</v>
       </c>
       <c r="BG11" t="n">
         <v>2</v>
@@ -6208,7 +6208,7 @@
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-1</v>
+        <v>25412</v>
       </c>
       <c r="BG12" t="n">
         <v>2</v>
@@ -6672,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-1</v>
+        <v>22210</v>
       </c>
       <c r="BG13" t="n">
         <v>2</v>
@@ -7116,7 +7116,7 @@
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-1</v>
+        <v>16367</v>
       </c>
       <c r="BG14" t="n">
         <v>2</v>
@@ -8044,7 +8044,7 @@
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-1</v>
+        <v>31606</v>
       </c>
       <c r="BG16" t="n">
         <v>-1</v>

--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL16" headerRowCount="1">
-  <autoFilter ref="A1:EL16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL27" headerRowCount="1">
+  <autoFilter ref="A1:EL27"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -270,20 +270,20 @@
     <tableColumn id="124" name="over45"/>
     <tableColumn id="125" name="over55"/>
     <tableColumn id="126" name="btts"/>
-    <tableColumn id="127" name="pinnacle_corners_over_95"/>
-    <tableColumn id="128" name="pinnacle_corners_under_95"/>
-    <tableColumn id="129" name="pinnacle_corners_over_85"/>
-    <tableColumn id="130" name="pinnacle_corners_under_85"/>
+    <tableColumn id="127" name="pinnacle_ft_1"/>
+    <tableColumn id="128" name="pinnacle_ft_x"/>
+    <tableColumn id="129" name="pinnacle_ft_2"/>
+    <tableColumn id="130" name="pinnacle_ft_over35"/>
     <tableColumn id="131" name="pinnacle_ft_over15"/>
     <tableColumn id="132" name="pinnacle_ft_over25"/>
-    <tableColumn id="133" name="pinnacle_ft_over35"/>
-    <tableColumn id="134" name="pinnacle_ft_1"/>
-    <tableColumn id="135" name="pinnacle_ft_x"/>
-    <tableColumn id="136" name="pinnacle_ft_2"/>
-    <tableColumn id="137" name="pinnacle_btts_no"/>
-    <tableColumn id="138" name="pinnacle_btts_yes"/>
-    <tableColumn id="139" name="pinnacle_1st_half_over15"/>
-    <tableColumn id="140" name="pinnacle_1st_half_under15"/>
+    <tableColumn id="133" name="pinnacle_btts_yes"/>
+    <tableColumn id="134" name="pinnacle_btts_no"/>
+    <tableColumn id="135" name="pinnacle_1st_half_under15"/>
+    <tableColumn id="136" name="pinnacle_1st_half_over15"/>
+    <tableColumn id="137" name="pinnacle_corners_over_95"/>
+    <tableColumn id="138" name="pinnacle_corners_under_95"/>
+    <tableColumn id="139" name="pinnacle_corners_over_85"/>
+    <tableColumn id="140" name="pinnacle_corners_under_85"/>
     <tableColumn id="141" name="pinnacle_1st_half_over05"/>
     <tableColumn id="142" name="pinnacle_1st_half_under05"/>
   </tableColumns>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL16"/>
+  <dimension ref="A1:EL27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -609,7 +609,7 @@
     <col width="16.8" customWidth="1" min="24" max="24"/>
     <col width="22.8" customWidth="1" min="25" max="25"/>
     <col width="22.8" customWidth="1" min="26" max="26"/>
-    <col width="26.4" customWidth="1" min="27" max="27"/>
+    <col width="27.6" customWidth="1" min="27" max="27"/>
     <col width="50" customWidth="1" min="28" max="28"/>
     <col width="21.6" customWidth="1" min="29" max="29"/>
     <col width="21.6" customWidth="1" min="30" max="30"/>
@@ -709,18 +709,18 @@
     <col width="9.6" customWidth="1" min="124" max="124"/>
     <col width="9.6" customWidth="1" min="125" max="125"/>
     <col width="8.4" customWidth="1" min="126" max="126"/>
-    <col width="31.2" customWidth="1" min="127" max="127"/>
-    <col width="32.4" customWidth="1" min="128" max="128"/>
-    <col width="31.2" customWidth="1" min="129" max="129"/>
-    <col width="32.4" customWidth="1" min="130" max="130"/>
+    <col width="18" customWidth="1" min="127" max="127"/>
+    <col width="18" customWidth="1" min="128" max="128"/>
+    <col width="18" customWidth="1" min="129" max="129"/>
+    <col width="24" customWidth="1" min="130" max="130"/>
     <col width="24" customWidth="1" min="131" max="131"/>
     <col width="24" customWidth="1" min="132" max="132"/>
-    <col width="24" customWidth="1" min="133" max="133"/>
-    <col width="18" customWidth="1" min="134" max="134"/>
-    <col width="18" customWidth="1" min="135" max="135"/>
-    <col width="18" customWidth="1" min="136" max="136"/>
-    <col width="21.6" customWidth="1" min="137" max="137"/>
-    <col width="22.8" customWidth="1" min="138" max="138"/>
+    <col width="22.8" customWidth="1" min="133" max="133"/>
+    <col width="21.6" customWidth="1" min="134" max="134"/>
+    <col width="32.4" customWidth="1" min="135" max="135"/>
+    <col width="31.2" customWidth="1" min="136" max="136"/>
+    <col width="31.2" customWidth="1" min="137" max="137"/>
+    <col width="32.4" customWidth="1" min="138" max="138"/>
     <col width="31.2" customWidth="1" min="139" max="139"/>
     <col width="32.4" customWidth="1" min="140" max="140"/>
     <col width="31.2" customWidth="1" min="141" max="141"/>
@@ -1360,72 +1360,72 @@
       </c>
       <c r="DW1" s="1" t="inlineStr">
         <is>
+          <t>pinnacle_ft_1</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_x</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_2</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_over35</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_over15</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_over25</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_btts_yes</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_btts_no</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_under15</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_over15</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
           <t>pinnacle_corners_over_95</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_corners_under_95</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_corners_over_85</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_corners_under_85</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_over15</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_over25</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_over35</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_1</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_x</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_2</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_btts_no</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_btts_yes</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_over15</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_under15</t>
         </is>
       </c>
       <c r="EK1" s="1" t="inlineStr">
@@ -1769,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="DE2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1824,54 +1824,54 @@
       </c>
       <c r="DW2" t="inlineStr">
         <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr"/>
+      <c r="EF2" t="inlineStr"/>
+      <c r="EG2" t="inlineStr">
+        <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>2.06</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr"/>
-      <c r="DZ2" t="inlineStr"/>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>3.58</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>1.56</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr"/>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2264,72 +2264,72 @@
       </c>
       <c r="DW3" t="inlineStr">
         <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
           <t>1.89</t>
         </is>
       </c>
-      <c r="DX3" t="inlineStr">
+      <c r="EH3" t="inlineStr">
         <is>
           <t>1.91</t>
         </is>
       </c>
-      <c r="DY3" t="inlineStr">
+      <c r="EI3" t="inlineStr">
         <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="DZ3" t="inlineStr">
+      <c r="EJ3" t="inlineStr">
         <is>
           <t>2.41</t>
-        </is>
-      </c>
-      <c r="EA3" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="EB3" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="EC3" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
-      </c>
-      <c r="ED3" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EE3" t="inlineStr">
-        <is>
-          <t>3.64</t>
-        </is>
-      </c>
-      <c r="EF3" t="inlineStr">
-        <is>
-          <t>3.77</t>
-        </is>
-      </c>
-      <c r="EG3" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="EH3" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EI3" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="EJ3" t="inlineStr">
-        <is>
-          <t>1.51</t>
         </is>
       </c>
       <c r="EK3" t="inlineStr"/>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -2366,86 +2366,78 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>6</v>
       </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T4" t="n">
         <v>9</v>
       </c>
       <c r="U4" t="n">
+        <v>17</v>
+      </c>
+      <c r="V4" t="n">
+        <v>22</v>
+      </c>
+      <c r="W4" t="n">
         <v>7</v>
       </c>
-      <c r="V4" t="n">
-        <v>12</v>
-      </c>
-      <c r="W4" t="n">
-        <v>16</v>
-      </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z4" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Audi Field</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>32-60 R Street South West, Buzzard Point, Washington, District of Columbia</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
         <v>1</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.28</v>
+        <v>1.69</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="AH4" t="n">
         <v>1.25</v>
@@ -2454,61 +2446,61 @@
         <v>1.73</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL4" t="n">
         <v>2.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AU4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB4" t="n">
-        <v>13401</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
@@ -2520,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>18003</v>
+        <v>24453</v>
       </c>
       <c r="BG4" t="n">
         <v>2</v>
@@ -2529,64 +2521,64 @@
         <v>1</v>
       </c>
       <c r="BI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BM4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BN4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
         <v>2</v>
       </c>
       <c r="BS4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU4" t="n">
         <v>1</v>
       </c>
       <c r="BV4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BW4" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="BX4" t="n">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="BY4" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.77</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.22</v>
+        <v>2.77</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.03</v>
+        <v>4.54</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2616,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
@@ -2634,28 +2626,28 @@
         <v>1</v>
       </c>
       <c r="CR4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="CS4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="CT4" t="n">
         <v>1</v>
       </c>
       <c r="CU4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CV4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="CW4" t="n">
         <v>1</v>
       </c>
       <c r="CX4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CY4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="CZ4" t="n">
         <v>0</v>
@@ -2670,10 +2662,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2709,10 +2701,10 @@
         <v>1</v>
       </c>
       <c r="DQ4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS4" t="b">
         <v>0</v>
@@ -2724,21 +2716,21 @@
         <v>0</v>
       </c>
       <c r="DV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="DZ4" t="inlineStr">
@@ -2748,62 +2740,62 @@
       </c>
       <c r="EA4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EB4" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EJ4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.26</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3200,66 +3192,66 @@
       </c>
       <c r="DW5" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>5.78</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>8.64</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr"/>
+      <c r="EF5" t="inlineStr"/>
+      <c r="EG5" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="DX5" t="inlineStr">
+      <c r="EH5" t="inlineStr">
         <is>
           <t>1.99</t>
         </is>
       </c>
-      <c r="DY5" t="inlineStr">
+      <c r="EI5" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="DZ5" t="inlineStr">
+      <c r="EJ5" t="inlineStr">
         <is>
           <t>2.56</t>
         </is>
       </c>
-      <c r="EA5" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="EB5" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EC5" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="ED5" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EE5" t="inlineStr">
-        <is>
-          <t>5.78</t>
-        </is>
-      </c>
-      <c r="EF5" t="inlineStr">
-        <is>
-          <t>8.64</t>
-        </is>
-      </c>
-      <c r="EG5" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
-      </c>
-      <c r="EH5" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EI5" t="inlineStr"/>
-      <c r="EJ5" t="inlineStr"/>
       <c r="EK5" t="inlineStr"/>
       <c r="EL5" t="inlineStr"/>
     </row>
@@ -3279,12 +3271,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -3294,78 +3286,86 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="n">
-        <v>9</v>
-      </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
         <v>6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>13</v>
-      </c>
-      <c r="S6" t="n">
-        <v>11</v>
       </c>
       <c r="T6" t="n">
         <v>9</v>
       </c>
       <c r="U6" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="V6" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="W6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z6" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Audi Field</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>32-60 R Street South West, Buzzard Point, Washington, District of Columbia</t>
+        </is>
+      </c>
       <c r="AC6" t="n">
         <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.69</v>
+        <v>3.28</v>
       </c>
       <c r="AF6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="n">
         <v>1.25</v>
@@ -3374,208 +3374,208 @@
         <v>1.73</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AL6" t="n">
         <v>2.1</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AO6" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AU6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB6" t="n">
+        <v>13401</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>18003</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
         <v>4</v>
       </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>24453</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BK6" t="n">
+      <c r="BM6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>105</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX6" t="n">
         <v>5</v>
       </c>
-      <c r="BL6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>66</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>87</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>120</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>26</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>10</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>7</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>8</v>
-      </c>
       <c r="CY6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="CZ6" t="n">
         <v>0</v>
@@ -3590,10 +3590,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DE6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3629,10 +3629,10 @@
         <v>1</v>
       </c>
       <c r="DQ6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS6" t="b">
         <v>0</v>
@@ -3644,86 +3644,86 @@
         <v>0</v>
       </c>
       <c r="DV6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW6" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="DX6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="DY6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="DZ6" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="EA6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EB6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EC6" t="inlineStr">
         <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
           <t>2.53</t>
         </is>
       </c>
-      <c r="ED6" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EE6" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="EF6" t="inlineStr">
-        <is>
-          <t>4.30</t>
-        </is>
-      </c>
-      <c r="EG6" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="EH6" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EI6" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
-      <c r="EJ6" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.85</t>
         </is>
       </c>
     </row>
@@ -3743,52 +3743,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
         <v>46075.0625</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
       </c>
       <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
         <v>5</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>8</v>
       </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>6</v>
@@ -3797,110 +3797,102 @@
         <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W7" t="n">
+        <v>16</v>
+      </c>
+      <c r="X7" t="n">
         <v>11</v>
       </c>
-      <c r="X7" t="n">
-        <v>20</v>
-      </c>
       <c r="Y7" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="Z7" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>BBVA Compass Stadium</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>2200 Texas Avenue, East End, Houston, Texas</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS7" t="n">
         <v>3.4</v>
       </c>
-      <c r="AG7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AT7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AU7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ7" t="n">
         <v>2</v>
       </c>
       <c r="BA7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>677447</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
@@ -3912,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>20254</v>
+        <v>25044</v>
       </c>
       <c r="BG7" t="n">
         <v>2</v>
@@ -3921,64 +3913,64 @@
         <v>1</v>
       </c>
       <c r="BI7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BK7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL7" t="n">
         <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
         <v>1</v>
       </c>
       <c r="BS7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU7" t="n">
         <v>1</v>
       </c>
       <c r="BV7" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="BW7" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="BX7" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="BY7" t="n">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.07</v>
+        <v>1.71</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="CB7" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4005,7 +3997,7 @@
         <v>1</v>
       </c>
       <c r="CK7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL7" t="n">
         <v>0</v>
@@ -4026,19 +4018,19 @@
         <v>1</v>
       </c>
       <c r="CR7" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="CS7" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="CT7" t="n">
         <v>1</v>
       </c>
       <c r="CU7" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="CV7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="CW7" t="n">
         <v>1</v>
@@ -4047,7 +4039,7 @@
         <v>4</v>
       </c>
       <c r="CY7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="CZ7" t="n">
         <v>0</v>
@@ -4095,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4107,10 +4099,10 @@
         <v>1</v>
       </c>
       <c r="DS7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU7" t="b">
         <v>0</v>
@@ -4120,66 +4112,74 @@
       </c>
       <c r="DW7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="DX7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="DY7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="DZ7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EA7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EB7" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
           <t>1.68</t>
         </is>
       </c>
-      <c r="EC7" t="inlineStr">
-        <is>
-          <t>2.64</t>
-        </is>
-      </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EI7" t="inlineStr"/>
-      <c r="EJ7" t="inlineStr"/>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI7" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EJ7" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
       <c r="EK7" t="inlineStr"/>
       <c r="EL7" t="inlineStr"/>
     </row>
@@ -4568,72 +4568,72 @@
       </c>
       <c r="DW8" t="inlineStr">
         <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EG8" t="inlineStr">
+        <is>
           <t>1.84</t>
         </is>
       </c>
-      <c r="DX8" t="inlineStr">
+      <c r="EH8" t="inlineStr">
         <is>
           <t>1.96</t>
         </is>
       </c>
-      <c r="DY8" t="inlineStr">
+      <c r="EI8" t="inlineStr">
         <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="DZ8" t="inlineStr">
+      <c r="EJ8" t="inlineStr">
         <is>
           <t>2.48</t>
-        </is>
-      </c>
-      <c r="EA8" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="EB8" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EC8" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="ED8" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="EE8" t="inlineStr">
-        <is>
-          <t>3.41</t>
-        </is>
-      </c>
-      <c r="EF8" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
-      <c r="EG8" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="EH8" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EI8" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="EJ8" t="inlineStr">
-        <is>
-          <t>1.43</t>
         </is>
       </c>
       <c r="EK8" t="inlineStr">
@@ -4663,22 +4663,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>46075.0625</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -4687,117 +4687,125 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
         <v>5</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X9" t="n">
         <v>11</v>
       </c>
       <c r="Y9" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z9" t="n">
         <v>55</v>
       </c>
-      <c r="Z9" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Toyota Stadium</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>6000 Main Street, Frisco, Texas</t>
+        </is>
+      </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU9" t="n">
         <v>5</v>
       </c>
       <c r="AV9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX9" t="n">
         <v>1</v>
@@ -4812,7 +4820,7 @@
         <v>3</v>
       </c>
       <c r="BB9" t="n">
-        <v>677447</v>
+        <v>13</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
@@ -4824,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>25044</v>
+        <v>11004</v>
       </c>
       <c r="BG9" t="n">
         <v>2</v>
@@ -4833,28 +4841,28 @@
         <v>1</v>
       </c>
       <c r="BI9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BM9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BN9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
@@ -4863,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT9" t="n">
         <v>1</v>
@@ -4872,25 +4880,25 @@
         <v>1</v>
       </c>
       <c r="BV9" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BW9" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="BX9" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="BY9" t="n">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.57</v>
+        <v>1.48</v>
       </c>
       <c r="CB9" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="CC9" t="n">
         <v>0</v>
@@ -4938,10 +4946,10 @@
         <v>1</v>
       </c>
       <c r="CR9" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="CS9" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="CT9" t="n">
         <v>1</v>
@@ -4950,7 +4958,7 @@
         <v>11</v>
       </c>
       <c r="CV9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CW9" t="n">
         <v>1</v>
@@ -4959,7 +4967,7 @@
         <v>4</v>
       </c>
       <c r="CY9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CZ9" t="n">
         <v>0</v>
@@ -4974,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
@@ -5007,7 +5015,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5032,76 +5040,84 @@
       </c>
       <c r="DW9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="DX9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="DY9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="DZ9" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="EA9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="EB9" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EJ9" t="inlineStr">
         <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="EK9" t="inlineStr"/>
-      <c r="EL9" t="inlineStr"/>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5119,164 +5135,164 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>46075.0625</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
         <v>5</v>
       </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7</v>
-      </c>
       <c r="L10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
         <v>10</v>
       </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="n">
-        <v>7</v>
-      </c>
-      <c r="U10" t="n">
-        <v>13</v>
-      </c>
       <c r="V10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="Y10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Toyota Stadium</t>
+          <t>BBVA Compass Stadium</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>6000 Main Street, Frisco, Texas</t>
+          <t>2200 Texas Avenue, East End, Houston, Texas</t>
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
         <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AF10" t="n">
         <v>3.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AM10" t="n">
         <v>1.44</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AO10" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AR10" t="n">
         <v>2.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AT10" t="n">
         <v>1.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
         <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>2</v>
       </c>
       <c r="BA10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB10" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
@@ -5288,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>11004</v>
+        <v>20254</v>
       </c>
       <c r="BG10" t="n">
         <v>2</v>
@@ -5297,22 +5313,22 @@
         <v>1</v>
       </c>
       <c r="BI10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BM10" t="n">
         <v>5</v>
       </c>
       <c r="BN10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BO10" t="n">
         <v>1</v>
@@ -5321,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR10" t="n">
         <v>1</v>
@@ -5330,31 +5346,31 @@
         <v>2</v>
       </c>
       <c r="BT10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU10" t="n">
         <v>1</v>
       </c>
       <c r="BV10" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="BW10" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BX10" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="BY10" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="CB10" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -5381,7 +5397,7 @@
         <v>1</v>
       </c>
       <c r="CK10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL10" t="n">
         <v>0</v>
@@ -5402,19 +5418,19 @@
         <v>1</v>
       </c>
       <c r="CR10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CS10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CT10" t="n">
         <v>1</v>
       </c>
       <c r="CU10" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV10" t="n">
         <v>11</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>18</v>
       </c>
       <c r="CW10" t="n">
         <v>1</v>
@@ -5423,7 +5439,7 @@
         <v>4</v>
       </c>
       <c r="CY10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CZ10" t="n">
         <v>0</v>
@@ -5438,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
@@ -5471,7 +5487,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5483,10 +5499,10 @@
         <v>1</v>
       </c>
       <c r="DS10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="b">
         <v>0</v>
@@ -5496,84 +5512,68 @@
       </c>
       <c r="DW10" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="DX10" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="DY10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="DZ10" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EA10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EB10" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
         <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EE10" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="EF10" t="inlineStr">
-        <is>
-          <t>3.73</t>
-        </is>
-      </c>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr"/>
+      <c r="EF10" t="inlineStr"/>
       <c r="EG10" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EJ10" t="inlineStr">
         <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EK10" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EL10" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr"/>
+      <c r="EL10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5960,72 +5960,72 @@
       </c>
       <c r="DW11" t="inlineStr">
         <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="DX11" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
+      </c>
+      <c r="DY11" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="DZ11" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EA11" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EB11" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EC11" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="ED11" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="EE11" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EF11" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EG11" t="inlineStr">
+        <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="DX11" t="inlineStr">
+      <c r="EH11" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="DY11" t="inlineStr">
+      <c r="EI11" t="inlineStr">
         <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="DZ11" t="inlineStr">
+      <c r="EJ11" t="inlineStr">
         <is>
           <t>2.28</t>
-        </is>
-      </c>
-      <c r="EA11" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="EB11" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EC11" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="ED11" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EE11" t="inlineStr">
-        <is>
-          <t>4.09</t>
-        </is>
-      </c>
-      <c r="EF11" t="inlineStr">
-        <is>
-          <t>3.57</t>
-        </is>
-      </c>
-      <c r="EG11" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
-      </c>
-      <c r="EH11" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EI11" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EJ11" t="inlineStr">
-        <is>
-          <t>1.71</t>
         </is>
       </c>
       <c r="EK11" t="inlineStr"/>
@@ -6416,72 +6416,72 @@
       </c>
       <c r="DW12" t="inlineStr">
         <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="DX12" t="inlineStr">
+        <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="DY12" t="inlineStr">
+        <is>
+          <t>5.58</t>
+        </is>
+      </c>
+      <c r="DZ12" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EA12" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EB12" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EC12" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="ED12" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EE12" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EF12" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EG12" t="inlineStr">
+        <is>
           <t>1.96</t>
         </is>
       </c>
-      <c r="DX12" t="inlineStr">
+      <c r="EH12" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="DY12" t="inlineStr">
+      <c r="EI12" t="inlineStr">
         <is>
           <t>1.57</t>
         </is>
       </c>
-      <c r="DZ12" t="inlineStr">
+      <c r="EJ12" t="inlineStr">
         <is>
           <t>2.30</t>
-        </is>
-      </c>
-      <c r="EA12" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="EB12" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="EC12" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="ED12" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EE12" t="inlineStr">
-        <is>
-          <t>4.62</t>
-        </is>
-      </c>
-      <c r="EF12" t="inlineStr">
-        <is>
-          <t>5.58</t>
-        </is>
-      </c>
-      <c r="EG12" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EH12" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EI12" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="EJ12" t="inlineStr">
-        <is>
-          <t>1.62</t>
         </is>
       </c>
       <c r="EK12" t="inlineStr"/>
@@ -6825,7 +6825,7 @@
         <v>3</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6855,7 +6855,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6880,60 +6880,60 @@
       </c>
       <c r="DW13" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="DX13" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="DY13" t="inlineStr">
         <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="DZ13" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="DZ13" t="inlineStr"/>
       <c r="EA13" t="inlineStr"/>
       <c r="EB13" t="inlineStr"/>
-      <c r="EC13" t="inlineStr"/>
+      <c r="EC13" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
       <c r="ED13" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="EE13" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EF13" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EG13" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EH13" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EI13" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EJ13" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EK13" t="inlineStr"/>
@@ -7299,7 +7299,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7324,72 +7324,72 @@
       </c>
       <c r="DW14" t="inlineStr">
         <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DX14" t="inlineStr">
+        <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="DY14" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="DZ14" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EA14" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EB14" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EC14" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="ED14" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EE14" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EF14" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EG14" t="inlineStr">
+        <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="DX14" t="inlineStr">
+      <c r="EH14" t="inlineStr">
         <is>
           <t>1.74</t>
         </is>
       </c>
-      <c r="DY14" t="inlineStr">
+      <c r="EI14" t="inlineStr">
         <is>
           <t>1.74</t>
         </is>
       </c>
-      <c r="DZ14" t="inlineStr">
+      <c r="EJ14" t="inlineStr">
         <is>
           <t>2.05</t>
-        </is>
-      </c>
-      <c r="EA14" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="EB14" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EC14" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="ED14" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="EE14" t="inlineStr">
-        <is>
-          <t>4.37</t>
-        </is>
-      </c>
-      <c r="EF14" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="EG14" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="EH14" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EI14" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="EJ14" t="inlineStr">
-        <is>
-          <t>1.71</t>
         </is>
       </c>
       <c r="EK14" t="inlineStr"/>
@@ -7722,7 +7722,7 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DE15" t="n">
         <v>1</v>
@@ -7780,72 +7780,72 @@
       </c>
       <c r="DW15" t="inlineStr">
         <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DX15" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="DY15" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="DZ15" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EA15" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EB15" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EC15" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="ED15" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EE15" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EF15" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EG15" t="inlineStr">
+        <is>
           <t>1.92</t>
         </is>
       </c>
-      <c r="DX15" t="inlineStr">
+      <c r="EH15" t="inlineStr">
         <is>
           <t>1.87</t>
         </is>
       </c>
-      <c r="DY15" t="inlineStr">
+      <c r="EI15" t="inlineStr">
         <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="DZ15" t="inlineStr">
+      <c r="EJ15" t="inlineStr">
         <is>
           <t>2.22</t>
-        </is>
-      </c>
-      <c r="EA15" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="EB15" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EC15" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="ED15" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EE15" t="inlineStr">
-        <is>
-          <t>3.73</t>
-        </is>
-      </c>
-      <c r="EF15" t="inlineStr">
-        <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="EG15" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="EH15" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EI15" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="EJ15" t="inlineStr">
-        <is>
-          <t>1.51</t>
         </is>
       </c>
       <c r="EK15" t="inlineStr">
@@ -8227,7 +8227,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8252,68 +8252,5024 @@
       </c>
       <c r="DW16" t="inlineStr">
         <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="DX16" t="inlineStr">
+        <is>
+          <t>5.53</t>
+        </is>
+      </c>
+      <c r="DY16" t="inlineStr">
+        <is>
+          <t>8.16</t>
+        </is>
+      </c>
+      <c r="DZ16" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EA16" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EB16" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EC16" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="ED16" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EE16" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EF16" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EG16" t="inlineStr">
+        <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="DX16" t="inlineStr">
+      <c r="EH16" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="DY16" t="inlineStr"/>
-      <c r="DZ16" t="inlineStr"/>
-      <c r="EA16" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="EB16" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EC16" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="ED16" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EE16" t="inlineStr">
-        <is>
-          <t>5.53</t>
-        </is>
-      </c>
-      <c r="EF16" t="inlineStr">
-        <is>
-          <t>8.16</t>
-        </is>
-      </c>
-      <c r="EG16" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="EH16" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EI16" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="EJ16" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
+      <c r="EI16" t="inlineStr"/>
+      <c r="EJ16" t="inlineStr"/>
       <c r="EK16" t="inlineStr"/>
       <c r="EL16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New York RB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>46081.8125</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>12</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>12</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Red Bull Arena</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Frank Rogers Boulevard South, Harrison, New Jersey</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>86</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>130</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>34</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP17" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW17" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="DX17" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="DY17" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="DZ17" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="EA17" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EB17" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EC17" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="ED17" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EE17" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EF17" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EG17" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH17" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EI17" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EJ17" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EK17" t="inlineStr"/>
+      <c r="EL17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Montreal Impact</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>46081.8125</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>12</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>11</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>17</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>12</v>
+      </c>
+      <c r="X18" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>33</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>67</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP18" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ18" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR18" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS18" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT18" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW18" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="DX18" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="DY18" t="inlineStr">
+        <is>
+          <t>5.77</t>
+        </is>
+      </c>
+      <c r="DZ18" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EA18" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EB18" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EC18" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="ED18" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EE18" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EF18" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EG18" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EH18" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EI18" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EJ18" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EK18" t="inlineStr"/>
+      <c r="EL18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>46081.89583333334</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>12</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>18</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>9</v>
+      </c>
+      <c r="U19" t="n">
+        <v>25</v>
+      </c>
+      <c r="V19" t="n">
+        <v>12</v>
+      </c>
+      <c r="W19" t="n">
+        <v>12</v>
+      </c>
+      <c r="X19" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP19" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ19" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR19" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS19" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT19" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU19" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV19" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW19" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="DX19" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="DY19" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="DZ19" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EA19" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EB19" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EC19" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="ED19" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EE19" t="inlineStr"/>
+      <c r="EF19" t="inlineStr"/>
+      <c r="EG19" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EH19" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EI19" t="inlineStr"/>
+      <c r="EJ19" t="inlineStr"/>
+      <c r="EK19" t="inlineStr"/>
+      <c r="EL19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>46081.89583333334</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12</v>
+      </c>
+      <c r="L20" t="n">
+        <v>17</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>11</v>
+      </c>
+      <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>16</v>
+      </c>
+      <c r="V20" t="n">
+        <v>13</v>
+      </c>
+      <c r="W20" t="n">
+        <v>9</v>
+      </c>
+      <c r="X20" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>63</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>127</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR20" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU20" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV20" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX20" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY20" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI20" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO20" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP20" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW20" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="DX20" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="DY20" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="DZ20" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EA20" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EB20" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EC20" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="ED20" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EE20" t="inlineStr"/>
+      <c r="EF20" t="inlineStr"/>
+      <c r="EG20" t="inlineStr"/>
+      <c r="EH20" t="inlineStr"/>
+      <c r="EI20" t="inlineStr"/>
+      <c r="EJ20" t="inlineStr"/>
+      <c r="EK20" t="inlineStr"/>
+      <c r="EL20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>46082.02083333334</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>11</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7</v>
+      </c>
+      <c r="U21" t="n">
+        <v>11</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR21" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU21" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV21" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX21" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY21" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ21" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA21" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB21" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC21" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD21" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF21" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH21" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ21" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DM21" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DN21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DO21" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP21" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ21" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR21" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS21" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT21" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU21" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV21" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW21" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DX21" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="DY21" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="DZ21" t="inlineStr"/>
+      <c r="EA21" t="inlineStr"/>
+      <c r="EB21" t="inlineStr"/>
+      <c r="EC21" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="ED21" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EE21" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EF21" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EG21" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EH21" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EI21" t="inlineStr"/>
+      <c r="EJ21" t="inlineStr"/>
+      <c r="EK21" t="inlineStr"/>
+      <c r="EL21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>46082.02083333334</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L22" t="n">
+        <v>15</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7</v>
+      </c>
+      <c r="S22" t="n">
+        <v>11</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>16</v>
+      </c>
+      <c r="V22" t="n">
+        <v>14</v>
+      </c>
+      <c r="W22" t="n">
+        <v>9</v>
+      </c>
+      <c r="X22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Rio Tinto Stadium</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>9256 South State Street, Sandy, Utah</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>64</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>123</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CB22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="CC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR22" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS22" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU22" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV22" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX22" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY22" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD22" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI22" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO22" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP22" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ22" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR22" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS22" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT22" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU22" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV22" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW22" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="DX22" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="DY22" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="DZ22" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EA22" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EB22" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EC22" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="ED22" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EE22" t="inlineStr"/>
+      <c r="EF22" t="inlineStr"/>
+      <c r="EG22" t="inlineStr"/>
+      <c r="EH22" t="inlineStr"/>
+      <c r="EI22" t="inlineStr"/>
+      <c r="EJ22" t="inlineStr"/>
+      <c r="EK22" t="inlineStr"/>
+      <c r="EL22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>46082.0625</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>12</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6</v>
+      </c>
+      <c r="S23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T23" t="n">
+        <v>12</v>
+      </c>
+      <c r="U23" t="n">
+        <v>12</v>
+      </c>
+      <c r="V23" t="n">
+        <v>18</v>
+      </c>
+      <c r="W23" t="n">
+        <v>7</v>
+      </c>
+      <c r="X23" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>71</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>BBVA Compass Stadium</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>2200 Texas Avenue, East End, Houston, Texas</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>6490</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>85</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>52</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>137</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CB23" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="CC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR23" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS23" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU23" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV23" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX23" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY23" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ23" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA23" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC23" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE23" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF23" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI23" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DO23" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP23" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ23" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW23" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="DX23" t="inlineStr">
+        <is>
+          <t>3.89</t>
+        </is>
+      </c>
+      <c r="DY23" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="DZ23" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EA23" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EB23" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EC23" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="ED23" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EE23" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EF23" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EG23" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EH23" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EI23" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EJ23" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EK23" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EL23" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>46082.0625</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>7</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>6</v>
+      </c>
+      <c r="X24" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Toyota Stadium</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>6000 Main Street, Frisco, Texas</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>69</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CB24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR24" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS24" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU24" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV24" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX24" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY24" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ24" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA24" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB24" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC24" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD24" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF24" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH24" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI24" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DO24" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW24" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="DX24" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="DY24" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="DZ24" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="EA24" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EB24" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EC24" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="ED24" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EE24" t="inlineStr"/>
+      <c r="EF24" t="inlineStr"/>
+      <c r="EG24" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH24" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EI24" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EJ24" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EK24" t="inlineStr"/>
+      <c r="EL24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>46082.0625</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>8</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>8</v>
+      </c>
+      <c r="V25" t="n">
+        <v>10</v>
+      </c>
+      <c r="W25" t="n">
+        <v>9</v>
+      </c>
+      <c r="X25" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Children's Mercy Park</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>One Sporting Way, Kansas City, Kansas</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>75</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>67</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>127</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CB25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR25" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS25" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU25" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV25" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX25" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY25" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ25" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA25" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB25" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC25" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DN25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DO25" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT25" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU25" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW25" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="DX25" t="inlineStr">
+        <is>
+          <t>4.48</t>
+        </is>
+      </c>
+      <c r="DY25" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DZ25" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EA25" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EB25" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EC25" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="ED25" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EE25" t="inlineStr"/>
+      <c r="EF25" t="inlineStr"/>
+      <c r="EG25" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EH25" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EI25" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EJ25" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EK25" t="inlineStr"/>
+      <c r="EL25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>46082.10416666666</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>10</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>11</v>
+      </c>
+      <c r="X26" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>BC Place Stadium</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>777 Pacific Boulevard, False Creek, Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>52</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CB26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR26" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS26" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU26" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV26" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX26" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY26" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ26" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA26" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB26" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC26" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD26" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF26" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH26" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ26" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK26" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DN26" t="n">
+        <v>3</v>
+      </c>
+      <c r="DO26" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP26" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ26" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR26" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW26" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="DX26" t="inlineStr">
+        <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="DY26" t="inlineStr">
+        <is>
+          <t>7.84</t>
+        </is>
+      </c>
+      <c r="DZ26" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EA26" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EB26" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EC26" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="ED26" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EE26" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EF26" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EG26" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EH26" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EI26" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EJ26" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EK26" t="inlineStr"/>
+      <c r="EL26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>46082.14583333334</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>9</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>12</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>14</v>
+      </c>
+      <c r="V27" t="n">
+        <v>4</v>
+      </c>
+      <c r="W27" t="n">
+        <v>7</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CB27" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR27" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS27" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU27" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV27" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX27" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY27" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA27" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC27" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD27" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ27" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DM27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DN27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DO27" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP27" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ27" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR27" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW27" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="DX27" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="DY27" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="DZ27" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EA27" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EB27" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EC27" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="ED27" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EE27" t="inlineStr"/>
+      <c r="EF27" t="inlineStr"/>
+      <c r="EG27" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EH27" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EI27" t="inlineStr"/>
+      <c r="EJ27" t="inlineStr"/>
+      <c r="EK27" t="inlineStr"/>
+      <c r="EL27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL27" headerRowCount="1">
-  <autoFilter ref="A1:EL27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL31" headerRowCount="1">
+  <autoFilter ref="A1:EL31"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL27"/>
+  <dimension ref="A1:EL31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -2836,89 +2836,89 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>5</v>
       </c>
       <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V5" t="n">
         <v>12</v>
       </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>8</v>
-      </c>
-      <c r="U5" t="n">
-        <v>13</v>
-      </c>
-      <c r="V5" t="n">
-        <v>10</v>
-      </c>
       <c r="W5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="X5" t="n">
         <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="Z5" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>BC Place Stadium</t>
+          <t>Audi Field</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>777 Pacific Boulevard, False Creek, Vancouver, British Columbia</t>
+          <t>32-60 R Street South West, Buzzard Point, Washington, District of Columbia</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.46</v>
+        <v>3.28</v>
       </c>
       <c r="AF5" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AK5" t="n">
         <v>1.65</v>
@@ -2930,7 +2930,7 @@
         <v>1.44</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AO5" t="n">
         <v>2.6</v>
@@ -2939,40 +2939,40 @@
         <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AU5" t="n">
         <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>13401</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
@@ -2984,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>23546</v>
+        <v>18003</v>
       </c>
       <c r="BG5" t="n">
         <v>2</v>
@@ -2993,64 +2993,64 @@
         <v>1</v>
       </c>
       <c r="BI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
         <v>4</v>
       </c>
-      <c r="BJ5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>2</v>
-      </c>
       <c r="BM5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BN5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR5" t="n">
         <v>2</v>
       </c>
       <c r="BS5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU5" t="n">
         <v>1</v>
       </c>
       <c r="BV5" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="BW5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="BX5" t="n">
         <v>104</v>
       </c>
       <c r="BY5" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="CA5" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="CB5" t="n">
-        <v>2.52</v>
+        <v>2.03</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO5" t="n">
         <v>0</v>
@@ -3098,28 +3098,28 @@
         <v>1</v>
       </c>
       <c r="CR5" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="CS5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="CT5" t="n">
         <v>1</v>
       </c>
       <c r="CU5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CV5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="CW5" t="n">
         <v>1</v>
       </c>
       <c r="CX5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="CZ5" t="n">
         <v>0</v>
@@ -3192,68 +3192,84 @@
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="DX5" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="DZ5" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>2.16</t>
-        </is>
-      </c>
-      <c r="EE5" t="inlineStr"/>
-      <c r="EF5" t="inlineStr"/>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
       <c r="EG5" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EJ5" t="inlineStr">
         <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="EK5" t="inlineStr"/>
-      <c r="EL5" t="inlineStr"/>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3271,12 +3287,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -3292,16 +3308,16 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -3310,71 +3326,71 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="V6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="X6" t="n">
         <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="Z6" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Audi Field</t>
+          <t>BC Place Stadium</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>32-60 R Street South West, Buzzard Point, Washington, District of Columbia</t>
+          <t>777 Pacific Boulevard, False Creek, Vancouver, British Columbia</t>
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.28</v>
+        <v>1.46</v>
       </c>
       <c r="AF6" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>6.55</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AK6" t="n">
         <v>1.65</v>
@@ -3386,7 +3402,7 @@
         <v>1.44</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AO6" t="n">
         <v>2.6</v>
@@ -3395,40 +3411,40 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AU6" t="n">
         <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>13401</v>
+        <v>5</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
@@ -3440,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>18003</v>
+        <v>23546</v>
       </c>
       <c r="BG6" t="n">
         <v>2</v>
@@ -3449,64 +3465,64 @@
         <v>1</v>
       </c>
       <c r="BI6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT6" t="n">
         <v>4</v>
       </c>
-      <c r="BM6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>3</v>
-      </c>
       <c r="BU6" t="n">
         <v>1</v>
       </c>
       <c r="BV6" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="BW6" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="BX6" t="n">
         <v>104</v>
       </c>
       <c r="BY6" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="CB6" t="n">
-        <v>2.03</v>
+        <v>2.52</v>
       </c>
       <c r="CC6" t="n">
         <v>0</v>
@@ -3542,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CO6" t="n">
         <v>0</v>
@@ -3554,28 +3570,28 @@
         <v>1</v>
       </c>
       <c r="CR6" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS6" t="n">
         <v>20</v>
       </c>
-      <c r="CS6" t="n">
-        <v>22</v>
-      </c>
       <c r="CT6" t="n">
         <v>1</v>
       </c>
       <c r="CU6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CV6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CW6" t="n">
         <v>1</v>
       </c>
       <c r="CX6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="CZ6" t="n">
         <v>0</v>
@@ -3623,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3648,84 +3664,68 @@
       </c>
       <c r="DW6" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="DX6" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="DY6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="DZ6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EA6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="EB6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EE6" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EF6" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr"/>
+      <c r="EF6" t="inlineStr"/>
       <c r="EG6" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EJ6" t="inlineStr">
         <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="EK6" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EL6" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr"/>
+      <c r="EL6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -4214,306 +4214,314 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>4</v>
       </c>
-      <c r="J8" t="n">
-        <v>7</v>
-      </c>
-      <c r="K8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>15</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" t="n">
         <v>6</v>
       </c>
-      <c r="R8" t="n">
-        <v>4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
       <c r="T8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
         <v>10</v>
       </c>
       <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
         <v>11</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>BBVA Compass Stadium</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2200 Texas Avenue, East End, Houston, Texas</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>20254</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>112</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY8" t="n">
         <v>8</v>
       </c>
-      <c r="X8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>57</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>43</v>
-      </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM8" t="n">
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
         <v>1.5</v>
       </c>
-      <c r="AN8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>20738</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>49</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>33</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>105</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>88</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>1</v>
-      </c>
       <c r="DE8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4543,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4555,7 +4563,7 @@
         <v>1</v>
       </c>
       <c r="DS8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT8" t="b">
         <v>0</v>
@@ -4568,84 +4576,68 @@
       </c>
       <c r="DW8" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="DX8" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="DY8" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="DZ8" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EA8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EB8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
         <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="EE8" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EF8" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr"/>
+      <c r="EF8" t="inlineStr"/>
       <c r="EG8" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EJ8" t="inlineStr">
         <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="EK8" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EL8" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EK8" t="inlineStr"/>
+      <c r="EL8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5135,12 +5127,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -5150,25 +5142,25 @@
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5177,270 +5169,262 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" t="n">
         <v>4</v>
       </c>
-      <c r="R10" t="n">
-        <v>3</v>
-      </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U10" t="n">
         <v>10</v>
       </c>
       <c r="V10" t="n">
+        <v>11</v>
+      </c>
+      <c r="W10" t="n">
+        <v>8</v>
+      </c>
+      <c r="X10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>20738</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>105</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX10" t="n">
         <v>6</v>
       </c>
-      <c r="W10" t="n">
-        <v>11</v>
-      </c>
-      <c r="X10" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>43</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>BBVA Compass Stadium</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>2200 Texas Avenue, East End, Houston, Texas</t>
-        </is>
-      </c>
-      <c r="AC10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB10" t="n">
+      <c r="CY10" t="n">
         <v>6</v>
       </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>20254</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>42</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>70</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>112</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>20</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>22</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ10" t="n">
         <v>0</v>
       </c>
@@ -5454,10 +5438,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DE10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5499,7 +5483,7 @@
         <v>1</v>
       </c>
       <c r="DS10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT10" t="b">
         <v>0</v>
@@ -5512,68 +5496,84 @@
       </c>
       <c r="DW10" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="DX10" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="DY10" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="DZ10" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EA10" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="EB10" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
         <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="EE10" t="inlineStr"/>
-      <c r="EF10" t="inlineStr"/>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
       <c r="EG10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EJ10" t="inlineStr">
         <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EK10" t="inlineStr"/>
-      <c r="EL10" t="inlineStr"/>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5905,7 +5905,7 @@
         <v>3</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6391,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6503,12 +6503,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -6518,25 +6518,25 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -6548,267 +6548,259 @@
         <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
+        <v>11</v>
+      </c>
+      <c r="T13" t="n">
         <v>6</v>
       </c>
-      <c r="T13" t="n">
-        <v>11</v>
-      </c>
       <c r="U13" t="n">
+        <v>17</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>14</v>
+      </c>
+      <c r="X13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>16367</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU13" t="n">
         <v>12</v>
       </c>
-      <c r="V13" t="n">
-        <v>15</v>
-      </c>
-      <c r="W13" t="n">
-        <v>4</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="CV13" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY13" t="n">
         <v>5</v>
       </c>
-      <c r="Y13" t="n">
-        <v>46</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>54</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Providence Park</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>1844 SW Morrison Street, Portland, Oregon</t>
-        </is>
-      </c>
-      <c r="AC13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>22210</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>37</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>70</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>98</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>111</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CB13" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="CC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>8</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>6</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>5</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>11</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ13" t="n">
         <v>0</v>
       </c>
@@ -6825,7 +6817,7 @@
         <v>3</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6867,73 +6859,85 @@
         <v>1</v>
       </c>
       <c r="DS13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="b">
         <v>0</v>
       </c>
       <c r="DV13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="DX13" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="DY13" t="inlineStr">
         <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="DZ13" t="inlineStr"/>
-      <c r="EA13" t="inlineStr"/>
-      <c r="EB13" t="inlineStr"/>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="DZ13" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EA13" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EB13" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
       <c r="EC13" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="ED13" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="EE13" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EF13" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EG13" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EH13" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EI13" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EJ13" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EK13" t="inlineStr"/>
@@ -6955,12 +6959,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -6970,25 +6974,25 @@
         <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7000,259 +7004,267 @@
         <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="n">
         <v>11</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
+        <v>12</v>
+      </c>
+      <c r="V14" t="n">
+        <v>15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4</v>
+      </c>
+      <c r="X14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Providence Park</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>1844 SW Morrison Street, Portland, Oregon</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>22210</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ14" t="n">
         <v>6</v>
       </c>
-      <c r="U14" t="n">
-        <v>17</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7</v>
-      </c>
-      <c r="W14" t="n">
-        <v>14</v>
-      </c>
-      <c r="X14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AN14" t="n">
+      <c r="BK14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CA14" t="n">
         <v>1.73</v>
       </c>
-      <c r="AO14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB14" t="n">
+      <c r="CB14" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS14" t="n">
         <v>15</v>
       </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>16367</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI14" t="n">
+      <c r="CT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU14" t="n">
         <v>6</v>
       </c>
-      <c r="BJ14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK14" t="n">
+      <c r="CV14" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY14" t="n">
         <v>9</v>
       </c>
-      <c r="BL14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>56</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>85</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>83</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="CC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU14" t="n">
-        <v>12</v>
-      </c>
-      <c r="CV14" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX14" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ14" t="n">
         <v>0</v>
       </c>
@@ -7269,7 +7281,7 @@
         <v>3</v>
       </c>
       <c r="DE14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7311,85 +7323,73 @@
         <v>1</v>
       </c>
       <c r="DS14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU14" t="b">
         <v>0</v>
       </c>
       <c r="DV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="DX14" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="DY14" t="inlineStr">
         <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="DZ14" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EA14" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="EB14" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="DZ14" t="inlineStr"/>
+      <c r="EA14" t="inlineStr"/>
+      <c r="EB14" t="inlineStr"/>
       <c r="EC14" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="ED14" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="EE14" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EF14" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EG14" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EH14" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EI14" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EJ14" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EK14" t="inlineStr"/>
@@ -7725,7 +7725,7 @@
         <v>2</v>
       </c>
       <c r="DE15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7755,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8500,7 +8500,7 @@
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-1</v>
+        <v>15087</v>
       </c>
       <c r="BG17" t="n">
         <v>2</v>
@@ -8956,7 +8956,7 @@
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>-1</v>
+        <v>20872</v>
       </c>
       <c r="BG18" t="n">
         <v>2</v>
@@ -9293,7 +9293,7 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
         <v>3</v>
@@ -9305,16 +9305,16 @@
         <v>9</v>
       </c>
       <c r="U19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V19" t="n">
         <v>12</v>
       </c>
       <c r="W19" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y19" t="n">
         <v>54</v>
@@ -9412,7 +9412,7 @@
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>-1</v>
+        <v>16113</v>
       </c>
       <c r="BG19" t="n">
         <v>-1</v>
@@ -9472,13 +9472,13 @@
         <v>83</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="CA19" t="n">
         <v>1.22</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>-1</v>
+        <v>19609</v>
       </c>
       <c r="BG20" t="n">
         <v>2</v>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -10138,25 +10138,25 @@
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L21" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -10168,90 +10168,98 @@
         <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T21" t="n">
         <v>7</v>
       </c>
       <c r="U21" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="W21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Z21" t="n">
-        <v>54</v>
-      </c>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Rio Tinto Stadium</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>9256 South State Street, Sandy, Utah</t>
+        </is>
+      </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AP21" t="n">
         <v>1.99</v>
       </c>
-      <c r="AF21" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>2</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AU21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -10263,16 +10271,16 @@
         <v>1</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA21" t="n">
         <v>1</v>
       </c>
       <c r="BB21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC21" t="n">
         <v>0</v>
@@ -10293,34 +10301,34 @@
         <v>1</v>
       </c>
       <c r="BI21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BK21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL21" t="n">
         <v>4</v>
       </c>
-      <c r="BL21" t="n">
-        <v>2</v>
-      </c>
       <c r="BM21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BN21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS21" t="n">
         <v>2</v>
@@ -10332,25 +10340,25 @@
         <v>1</v>
       </c>
       <c r="BV21" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BW21" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="BX21" t="n">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="BY21" t="n">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="CA21" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.81</v>
       </c>
       <c r="CB21" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="CC21" t="n">
         <v>0</v>
@@ -10383,31 +10391,31 @@
         <v>0</v>
       </c>
       <c r="CM21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN21" t="n">
         <v>0</v>
       </c>
       <c r="CO21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ21" t="n">
         <v>1</v>
       </c>
       <c r="CR21" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CS21" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="CT21" t="n">
         <v>1</v>
       </c>
       <c r="CU21" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="CV21" t="n">
         <v>9</v>
@@ -10416,22 +10424,22 @@
         <v>1</v>
       </c>
       <c r="CX21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CY21" t="n">
         <v>9</v>
       </c>
       <c r="CZ21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DB21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DD21" t="n">
         <v>3</v>
@@ -10440,31 +10448,31 @@
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DG21" t="n">
         <v>0</v>
       </c>
       <c r="DH21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DI21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DJ21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK21" t="n">
         <v>0</v>
       </c>
       <c r="DL21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="DM21" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="DN21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="DO21" t="n">
         <v>2</v>
@@ -10476,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="DR21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS21" t="b">
         <v>0</v>
@@ -10488,56 +10496,52 @@
         <v>0</v>
       </c>
       <c r="DV21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW21" t="inlineStr">
         <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="DX21" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="DY21" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="DZ21" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EA21" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EB21" t="inlineStr">
+        <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="DX21" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="DY21" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="DZ21" t="inlineStr"/>
-      <c r="EA21" t="inlineStr"/>
-      <c r="EB21" t="inlineStr"/>
       <c r="EC21" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="ED21" t="inlineStr">
         <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="EE21" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EF21" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="EG21" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EH21" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EE21" t="inlineStr"/>
+      <c r="EF21" t="inlineStr"/>
+      <c r="EG21" t="inlineStr"/>
+      <c r="EH21" t="inlineStr"/>
       <c r="EI21" t="inlineStr"/>
       <c r="EJ21" t="inlineStr"/>
       <c r="EK21" t="inlineStr"/>
@@ -10559,12 +10563,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -10574,25 +10578,25 @@
         <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -10604,98 +10608,90 @@
         <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T22" t="n">
         <v>7</v>
       </c>
       <c r="U22" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V22" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="W22" t="n">
         <v>9</v>
       </c>
       <c r="X22" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="Y22" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="Z22" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Rio Tinto Stadium</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>9256 South State Street, Sandy, Utah</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>3.1</v>
+        <v>1.99</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.1</v>
+        <v>3.37</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.25</v>
+        <v>2.31</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AO22" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AU22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV22" t="n">
         <v>1</v>
@@ -10707,16 +10703,16 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA22" t="n">
         <v>1</v>
       </c>
       <c r="BB22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC22" t="n">
         <v>0</v>
@@ -10737,34 +10733,34 @@
         <v>1</v>
       </c>
       <c r="BI22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN22" t="n">
         <v>6</v>
       </c>
-      <c r="BK22" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>7</v>
-      </c>
       <c r="BO22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS22" t="n">
         <v>2</v>
@@ -10776,25 +10772,25 @@
         <v>1</v>
       </c>
       <c r="BV22" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BW22" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="BX22" t="n">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="BY22" t="n">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="CC22" t="n">
         <v>0</v>
@@ -10827,31 +10823,31 @@
         <v>0</v>
       </c>
       <c r="CM22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN22" t="n">
         <v>0</v>
       </c>
       <c r="CO22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ22" t="n">
         <v>1</v>
       </c>
       <c r="CR22" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="CS22" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="CT22" t="n">
         <v>1</v>
       </c>
       <c r="CU22" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="CV22" t="n">
         <v>9</v>
@@ -10860,22 +10856,22 @@
         <v>1</v>
       </c>
       <c r="CX22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CY22" t="n">
         <v>9</v>
       </c>
       <c r="CZ22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DB22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD22" t="n">
         <v>3</v>
@@ -10884,31 +10880,31 @@
         <v>0</v>
       </c>
       <c r="DF22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG22" t="n">
         <v>0</v>
       </c>
       <c r="DH22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DI22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK22" t="n">
         <v>0</v>
       </c>
       <c r="DL22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="DM22" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="DN22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="DO22" t="n">
         <v>2</v>
@@ -10920,7 +10916,7 @@
         <v>1</v>
       </c>
       <c r="DR22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS22" t="b">
         <v>0</v>
@@ -10932,52 +10928,56 @@
         <v>0</v>
       </c>
       <c r="DV22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW22" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="DX22" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="DY22" t="inlineStr">
         <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="DZ22" t="inlineStr"/>
+      <c r="EA22" t="inlineStr"/>
+      <c r="EB22" t="inlineStr"/>
+      <c r="EC22" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="ED22" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EE22" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EF22" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EG22" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EH22" t="inlineStr">
+        <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="DZ22" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
-      <c r="EA22" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EB22" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EC22" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="ED22" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="EE22" t="inlineStr"/>
-      <c r="EF22" t="inlineStr"/>
-      <c r="EG22" t="inlineStr"/>
-      <c r="EH22" t="inlineStr"/>
       <c r="EI22" t="inlineStr"/>
       <c r="EJ22" t="inlineStr"/>
       <c r="EK22" t="inlineStr"/>
@@ -11294,7 +11294,7 @@
         <v>14</v>
       </c>
       <c r="CV23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CW23" t="n">
         <v>1</v>
@@ -11492,13 +11492,13 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M24" t="n">
         <v>3</v>
@@ -11519,16 +11519,16 @@
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U24" t="n">
+        <v>9</v>
+      </c>
+      <c r="V24" t="n">
         <v>7</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6</v>
       </c>
       <c r="W24" t="n">
         <v>6</v>
@@ -11537,10 +11537,10 @@
         <v>9</v>
       </c>
       <c r="Y24" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Z24" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -11700,13 +11700,13 @@
         <v>69</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0.85</v>
+        <v>0.97</v>
       </c>
       <c r="CA24" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="CB24" t="n">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="CC24" t="n">
         <v>0</v>
@@ -11754,28 +11754,28 @@
         <v>1</v>
       </c>
       <c r="CR24" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS24" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU24" t="n">
         <v>15</v>
       </c>
-      <c r="CS24" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT24" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU24" t="n">
-        <v>12</v>
-      </c>
       <c r="CV24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CW24" t="n">
         <v>1</v>
       </c>
       <c r="CX24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CZ24" t="n">
         <v>50</v>
@@ -12425,19 +12425,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V26" t="n">
         <v>5</v>
@@ -12612,13 +12612,13 @@
         <v>52</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="CA26" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="CB26" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="CC26" t="n">
         <v>1</v>
@@ -12666,28 +12666,28 @@
         <v>1</v>
       </c>
       <c r="CR26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="CS26" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="CT26" t="n">
         <v>1</v>
       </c>
       <c r="CU26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CV26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CW26" t="n">
         <v>1</v>
       </c>
       <c r="CX26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CY26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ26" t="n">
         <v>50</v>
@@ -13216,42 +13216,42 @@
       </c>
       <c r="DW27" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="DX27" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="DY27" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="DZ27" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EA27" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EB27" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EC27" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="ED27" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="EE27" t="inlineStr"/>
@@ -13270,6 +13270,1814 @@
       <c r="EJ27" t="inlineStr"/>
       <c r="EK27" t="inlineStr"/>
       <c r="EL27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>46082.8125</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>10</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>14</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>9</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>9</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>18</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>14</v>
+      </c>
+      <c r="X28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>698284</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="CB28" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM28" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR28" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS28" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU28" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV28" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX28" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY28" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ28" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA28" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB28" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC28" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD28" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF28" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI28" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DO28" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP28" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW28" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DX28" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="DY28" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="DZ28" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EA28" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EB28" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EC28" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="ED28" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EE28" t="inlineStr"/>
+      <c r="EF28" t="inlineStr"/>
+      <c r="EG28" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EH28" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EI28" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EJ28" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EK28" t="inlineStr"/>
+      <c r="EL28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>46082.89583333334</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>9</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>9</v>
+      </c>
+      <c r="S29" t="n">
+        <v>11</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>16</v>
+      </c>
+      <c r="V29" t="n">
+        <v>13</v>
+      </c>
+      <c r="W29" t="n">
+        <v>11</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>18513</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>86</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB29" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="CC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR29" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS29" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU29" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX29" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY29" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA29" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC29" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE29" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG29" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ29" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DN29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DO29" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP29" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ29" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR29" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV29" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW29" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="DX29" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="DY29" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="DZ29" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="EA29" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EB29" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EC29" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="ED29" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EE29" t="inlineStr"/>
+      <c r="EF29" t="inlineStr"/>
+      <c r="EG29" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH29" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EI29" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EJ29" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EK29" t="inlineStr"/>
+      <c r="EL29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>10</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>8</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>7</v>
+      </c>
+      <c r="U30" t="n">
+        <v>10</v>
+      </c>
+      <c r="V30" t="n">
+        <v>15</v>
+      </c>
+      <c r="W30" t="n">
+        <v>16</v>
+      </c>
+      <c r="X30" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>677446</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>24453</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>100</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CB30" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR30" t="n">
+        <v>9</v>
+      </c>
+      <c r="CS30" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU30" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV30" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX30" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY30" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ30" t="n">
+        <v>100</v>
+      </c>
+      <c r="DA30" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC30" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DM30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DN30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="DO30" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP30" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ30" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR30" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS30" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT30" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU30" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV30" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW30" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="DX30" t="inlineStr">
+        <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="DY30" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="DZ30" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EA30" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="EB30" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EC30" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="ED30" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EE30" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EF30" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG30" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EH30" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EI30" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EJ30" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EK30" t="inlineStr"/>
+      <c r="EL30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>46083.09375</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>10</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6</v>
+      </c>
+      <c r="W31" t="n">
+        <v>9</v>
+      </c>
+      <c r="X31" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1398748</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>62</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>52</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CB31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR31" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS31" t="n">
+        <v>8</v>
+      </c>
+      <c r="CT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU31" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV31" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX31" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY31" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ31" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA31" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB31" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC31" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD31" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF31" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH31" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DO31" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP31" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ31" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR31" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS31" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT31" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU31" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV31" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW31" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="DX31" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="DY31" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="DZ31" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EA31" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EB31" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EC31" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="ED31" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EE31" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EF31" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EG31" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EH31" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EI31" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EJ31" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EK31" t="inlineStr"/>
+      <c r="EL31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -12552,7 +12552,7 @@
         <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>-1</v>
+        <v>24533</v>
       </c>
       <c r="BG26" t="n">
         <v>2</v>
@@ -13448,7 +13448,7 @@
         <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>-1</v>
+        <v>20738</v>
       </c>
       <c r="BG28" t="n">
         <v>2</v>
@@ -14800,7 +14800,7 @@
         <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>-1</v>
+        <v>21969</v>
       </c>
       <c r="BG31" t="n">
         <v>2</v>

--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL31" headerRowCount="1">
-  <autoFilter ref="A1:EL31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL32" headerRowCount="1">
+  <autoFilter ref="A1:EL32"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -278,12 +278,12 @@
     <tableColumn id="132" name="pinnacle_ft_over25"/>
     <tableColumn id="133" name="pinnacle_btts_yes"/>
     <tableColumn id="134" name="pinnacle_btts_no"/>
-    <tableColumn id="135" name="pinnacle_1st_half_under15"/>
-    <tableColumn id="136" name="pinnacle_1st_half_over15"/>
-    <tableColumn id="137" name="pinnacle_corners_over_95"/>
-    <tableColumn id="138" name="pinnacle_corners_under_95"/>
-    <tableColumn id="139" name="pinnacle_corners_over_85"/>
-    <tableColumn id="140" name="pinnacle_corners_under_85"/>
+    <tableColumn id="135" name="pinnacle_corners_over_95"/>
+    <tableColumn id="136" name="pinnacle_corners_over_85"/>
+    <tableColumn id="137" name="pinnacle_corners_under_95"/>
+    <tableColumn id="138" name="pinnacle_corners_under_85"/>
+    <tableColumn id="139" name="pinnacle_1st_half_under15"/>
+    <tableColumn id="140" name="pinnacle_1st_half_over15"/>
     <tableColumn id="141" name="pinnacle_1st_half_over05"/>
     <tableColumn id="142" name="pinnacle_1st_half_under05"/>
   </tableColumns>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL31"/>
+  <dimension ref="A1:EL32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -717,12 +717,12 @@
     <col width="24" customWidth="1" min="132" max="132"/>
     <col width="22.8" customWidth="1" min="133" max="133"/>
     <col width="21.6" customWidth="1" min="134" max="134"/>
-    <col width="32.4" customWidth="1" min="135" max="135"/>
+    <col width="31.2" customWidth="1" min="135" max="135"/>
     <col width="31.2" customWidth="1" min="136" max="136"/>
-    <col width="31.2" customWidth="1" min="137" max="137"/>
+    <col width="32.4" customWidth="1" min="137" max="137"/>
     <col width="32.4" customWidth="1" min="138" max="138"/>
-    <col width="31.2" customWidth="1" min="139" max="139"/>
-    <col width="32.4" customWidth="1" min="140" max="140"/>
+    <col width="32.4" customWidth="1" min="139" max="139"/>
+    <col width="31.2" customWidth="1" min="140" max="140"/>
     <col width="31.2" customWidth="1" min="141" max="141"/>
     <col width="32.4" customWidth="1" min="142" max="142"/>
   </cols>
@@ -1400,32 +1400,32 @@
       </c>
       <c r="EE1" s="1" t="inlineStr">
         <is>
+          <t>pinnacle_corners_over_95</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_corners_over_85</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_corners_under_95</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_corners_under_85</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
           <t>pinnacle_1st_half_under15</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_1st_half_over15</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_corners_over_95</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_corners_under_95</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_corners_over_85</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_corners_under_85</t>
         </is>
       </c>
       <c r="EK1" s="1" t="inlineStr">
@@ -1862,18 +1862,18 @@
           <t>2.48</t>
         </is>
       </c>
-      <c r="EE2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
       <c r="EF2" t="inlineStr"/>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
           <t>2.06</t>
         </is>
       </c>
+      <c r="EH2" t="inlineStr"/>
       <c r="EI2" t="inlineStr"/>
       <c r="EJ2" t="inlineStr"/>
       <c r="EK2" t="inlineStr"/>
@@ -2304,32 +2304,32 @@
       </c>
       <c r="EE3" t="inlineStr">
         <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="EF3" t="inlineStr">
+      <c r="EJ3" t="inlineStr">
         <is>
           <t>2.62</t>
-        </is>
-      </c>
-      <c r="EG3" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EH3" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="EI3" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EJ3" t="inlineStr">
-        <is>
-          <t>2.41</t>
         </is>
       </c>
       <c r="EK3" t="inlineStr"/>
@@ -2760,32 +2760,32 @@
       </c>
       <c r="EE4" t="inlineStr">
         <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="EF4" t="inlineStr">
+      <c r="EJ4" t="inlineStr">
         <is>
           <t>2.44</t>
-        </is>
-      </c>
-      <c r="EG4" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EH4" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EI4" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EJ4" t="inlineStr">
-        <is>
-          <t>2.21</t>
         </is>
       </c>
       <c r="EK4" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -2836,16 +2836,16 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
         <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -2854,71 +2854,71 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="V5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="X5" t="n">
         <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="Z5" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Audi Field</t>
+          <t>BC Place Stadium</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>32-60 R Street South West, Buzzard Point, Washington, District of Columbia</t>
+          <t>777 Pacific Boulevard, False Creek, Vancouver, British Columbia</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.28</v>
+        <v>1.46</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>6.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AK5" t="n">
         <v>1.65</v>
@@ -2930,7 +2930,7 @@
         <v>1.44</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AO5" t="n">
         <v>2.6</v>
@@ -2939,40 +2939,40 @@
         <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AU5" t="n">
         <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>13401</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
@@ -2984,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>18003</v>
+        <v>23546</v>
       </c>
       <c r="BG5" t="n">
         <v>2</v>
@@ -2993,64 +2993,64 @@
         <v>1</v>
       </c>
       <c r="BI5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT5" t="n">
         <v>4</v>
       </c>
-      <c r="BM5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>3</v>
-      </c>
       <c r="BU5" t="n">
         <v>1</v>
       </c>
       <c r="BV5" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="BW5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="BX5" t="n">
         <v>104</v>
       </c>
       <c r="BY5" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="CB5" t="n">
-        <v>2.03</v>
+        <v>2.52</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CO5" t="n">
         <v>0</v>
@@ -3098,28 +3098,28 @@
         <v>1</v>
       </c>
       <c r="CR5" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS5" t="n">
         <v>20</v>
       </c>
-      <c r="CS5" t="n">
-        <v>22</v>
-      </c>
       <c r="CT5" t="n">
         <v>1</v>
       </c>
       <c r="CU5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CV5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CW5" t="n">
         <v>1</v>
       </c>
       <c r="CX5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="CZ5" t="n">
         <v>0</v>
@@ -3192,84 +3192,68 @@
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="DX5" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="DZ5" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EI5" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EJ5" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="EK5" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EL5" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr"/>
+      <c r="EJ5" t="inlineStr"/>
+      <c r="EK5" t="inlineStr"/>
+      <c r="EL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3287,12 +3271,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -3308,89 +3292,89 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
       </c>
       <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>9</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7</v>
+      </c>
+      <c r="V6" t="n">
         <v>12</v>
       </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>8</v>
-      </c>
-      <c r="U6" t="n">
-        <v>13</v>
-      </c>
-      <c r="V6" t="n">
-        <v>10</v>
-      </c>
       <c r="W6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="X6" t="n">
         <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="Z6" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>BC Place Stadium</t>
+          <t>Audi Field</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>777 Pacific Boulevard, False Creek, Vancouver, British Columbia</t>
+          <t>32-60 R Street South West, Buzzard Point, Washington, District of Columbia</t>
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.46</v>
+        <v>3.28</v>
       </c>
       <c r="AF6" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>6.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AK6" t="n">
         <v>1.65</v>
@@ -3402,7 +3386,7 @@
         <v>1.44</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AO6" t="n">
         <v>2.6</v>
@@ -3411,40 +3395,40 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AU6" t="n">
         <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB6" t="n">
-        <v>5</v>
+        <v>13401</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
@@ -3456,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>23546</v>
+        <v>18003</v>
       </c>
       <c r="BG6" t="n">
         <v>2</v>
@@ -3465,64 +3449,64 @@
         <v>1</v>
       </c>
       <c r="BI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
         <v>4</v>
       </c>
-      <c r="BJ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>2</v>
-      </c>
       <c r="BM6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BN6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BO6" t="n">
         <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR6" t="n">
         <v>2</v>
       </c>
       <c r="BS6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU6" t="n">
         <v>1</v>
       </c>
       <c r="BV6" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="BW6" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="BX6" t="n">
         <v>104</v>
       </c>
       <c r="BY6" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="CA6" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="CB6" t="n">
-        <v>2.52</v>
+        <v>2.03</v>
       </c>
       <c r="CC6" t="n">
         <v>0</v>
@@ -3558,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO6" t="n">
         <v>0</v>
@@ -3570,28 +3554,28 @@
         <v>1</v>
       </c>
       <c r="CR6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="CS6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="CT6" t="n">
         <v>1</v>
       </c>
       <c r="CU6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CV6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="CW6" t="n">
         <v>1</v>
       </c>
       <c r="CX6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="CZ6" t="n">
         <v>0</v>
@@ -3664,68 +3648,84 @@
       </c>
       <c r="DW6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="DX6" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="DY6" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="DZ6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="EA6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EB6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>2.16</t>
-        </is>
-      </c>
-      <c r="EE6" t="inlineStr"/>
-      <c r="EF6" t="inlineStr"/>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
       <c r="EG6" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EJ6" t="inlineStr">
         <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="EK6" t="inlineStr"/>
-      <c r="EL6" t="inlineStr"/>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4152,32 +4152,32 @@
       </c>
       <c r="EE7" t="inlineStr">
         <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EF7" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EG7" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EI7" t="inlineStr">
+        <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="EF7" t="inlineStr">
+      <c r="EJ7" t="inlineStr">
         <is>
           <t>2.39</t>
-        </is>
-      </c>
-      <c r="EG7" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EH7" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EI7" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EJ7" t="inlineStr">
-        <is>
-          <t>2.31</t>
         </is>
       </c>
       <c r="EK7" t="inlineStr"/>
@@ -4614,28 +4614,28 @@
           <t>2.52</t>
         </is>
       </c>
-      <c r="EE8" t="inlineStr"/>
-      <c r="EF8" t="inlineStr"/>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
       <c r="EG8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EI8" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EJ8" t="inlineStr">
-        <is>
           <t>2.55</t>
         </is>
       </c>
+      <c r="EI8" t="inlineStr"/>
+      <c r="EJ8" t="inlineStr"/>
       <c r="EK8" t="inlineStr"/>
       <c r="EL8" t="inlineStr"/>
     </row>
@@ -5072,32 +5072,32 @@
       </c>
       <c r="EE9" t="inlineStr">
         <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr">
+        <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="EF9" t="inlineStr">
+      <c r="EJ9" t="inlineStr">
         <is>
           <t>2.65</t>
-        </is>
-      </c>
-      <c r="EG9" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="EH9" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="EI9" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EJ9" t="inlineStr">
-        <is>
-          <t>2.38</t>
         </is>
       </c>
       <c r="EK9" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="EE10" t="inlineStr">
         <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="EF10" t="inlineStr">
+      <c r="EJ10" t="inlineStr">
         <is>
           <t>2.88</t>
-        </is>
-      </c>
-      <c r="EG10" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EH10" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EI10" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EJ10" t="inlineStr">
-        <is>
-          <t>2.48</t>
         </is>
       </c>
       <c r="EK10" t="inlineStr">
@@ -6000,32 +6000,32 @@
       </c>
       <c r="EE11" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EF11" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EG11" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EH11" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EI11" t="inlineStr">
+        <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="EF11" t="inlineStr">
+      <c r="EJ11" t="inlineStr">
         <is>
           <t>2.18</t>
-        </is>
-      </c>
-      <c r="EG11" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EH11" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EI11" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EJ11" t="inlineStr">
-        <is>
-          <t>2.28</t>
         </is>
       </c>
       <c r="EK11" t="inlineStr"/>
@@ -6047,132 +6047,140 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
         <v>46075.14583333334</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
       </c>
       <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>12</v>
+      </c>
+      <c r="V12" t="n">
+        <v>15</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4</v>
+      </c>
+      <c r="X12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>7</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>10</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>9</v>
-      </c>
-      <c r="X12" t="n">
-        <v>11</v>
-      </c>
       <c r="Y12" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="Z12" t="n">
-        <v>31</v>
-      </c>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Providence Park</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>1844 SW Morrison Street, Portland, Oregon</t>
+        </is>
+      </c>
       <c r="AC12" t="n">
         <v>1</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.37</v>
+        <v>2.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AK12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM12" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AN12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AO12" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AU12" t="n">
         <v>5</v>
@@ -6181,22 +6189,22 @@
         <v>2</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB12" t="n">
-        <v>1398748</v>
+        <v>20</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
@@ -6208,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>25412</v>
+        <v>22210</v>
       </c>
       <c r="BG12" t="n">
         <v>2</v>
@@ -6220,28 +6228,28 @@
         <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BK12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN12" t="n">
         <v>5</v>
       </c>
-      <c r="BN12" t="n">
-        <v>2</v>
-      </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>1</v>
@@ -6250,31 +6258,31 @@
         <v>1</v>
       </c>
       <c r="BT12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU12" t="n">
         <v>1</v>
       </c>
       <c r="BV12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="BW12" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="BX12" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="BY12" t="n">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="CB12" t="n">
-        <v>2.06</v>
+        <v>3.19</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6304,46 +6312,46 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM12" t="n">
         <v>1</v>
       </c>
       <c r="CN12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO12" t="n">
         <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ12" t="n">
         <v>1</v>
       </c>
       <c r="CR12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CS12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CT12" t="n">
         <v>1</v>
       </c>
       <c r="CU12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="CV12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="CW12" t="n">
         <v>1</v>
       </c>
       <c r="CX12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="CY12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="CZ12" t="n">
         <v>0</v>
@@ -6361,7 +6369,7 @@
         <v>3</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6412,76 +6420,64 @@
         <v>0</v>
       </c>
       <c r="DV12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="DX12" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="DY12" t="inlineStr">
         <is>
-          <t>5.58</t>
-        </is>
-      </c>
-      <c r="DZ12" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="EA12" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="EB12" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="DZ12" t="inlineStr"/>
+      <c r="EA12" t="inlineStr"/>
+      <c r="EB12" t="inlineStr"/>
       <c r="EC12" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="ED12" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="EE12" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EF12" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EG12" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EH12" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EI12" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="EF12" t="inlineStr">
+      <c r="EJ12" t="inlineStr">
         <is>
           <t>2.34</t>
-        </is>
-      </c>
-      <c r="EG12" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EH12" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EI12" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EJ12" t="inlineStr">
-        <is>
-          <t>2.30</t>
         </is>
       </c>
       <c r="EK12" t="inlineStr"/>
@@ -6912,32 +6908,32 @@
       </c>
       <c r="EE13" t="inlineStr">
         <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EF13" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EG13" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EH13" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EI13" t="inlineStr">
+        <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="EF13" t="inlineStr">
+      <c r="EJ13" t="inlineStr">
         <is>
           <t>2.17</t>
-        </is>
-      </c>
-      <c r="EG13" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="EH13" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EI13" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EJ13" t="inlineStr">
-        <is>
-          <t>2.05</t>
         </is>
       </c>
       <c r="EK13" t="inlineStr"/>
@@ -6959,140 +6955,132 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
         <v>46075.14583333334</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>5</v>
       </c>
       <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>10</v>
+      </c>
+      <c r="V14" t="n">
         <v>6</v>
       </c>
-      <c r="K14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" t="n">
-        <v>14</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>6</v>
-      </c>
-      <c r="T14" t="n">
+      <c r="W14" t="n">
+        <v>9</v>
+      </c>
+      <c r="X14" t="n">
         <v>11</v>
       </c>
-      <c r="U14" t="n">
-        <v>12</v>
-      </c>
-      <c r="V14" t="n">
-        <v>15</v>
-      </c>
-      <c r="W14" t="n">
-        <v>4</v>
-      </c>
-      <c r="X14" t="n">
-        <v>5</v>
-      </c>
       <c r="Y14" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="Z14" t="n">
-        <v>54</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Providence Park</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>1844 SW Morrison Street, Portland, Oregon</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
         <v>1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>1.37</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AO14" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AU14" t="n">
         <v>5</v>
@@ -7101,22 +7089,22 @@
         <v>2</v>
       </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>20</v>
+        <v>1398748</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
@@ -7128,7 +7116,7 @@
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>22210</v>
+        <v>25412</v>
       </c>
       <c r="BG14" t="n">
         <v>2</v>
@@ -7140,28 +7128,28 @@
         <v>3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BK14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BN14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BO14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR14" t="n">
         <v>1</v>
@@ -7170,31 +7158,31 @@
         <v>1</v>
       </c>
       <c r="BT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU14" t="n">
         <v>1</v>
       </c>
       <c r="BV14" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="BW14" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="BX14" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="BY14" t="n">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.19</v>
+        <v>2.06</v>
       </c>
       <c r="CC14" t="n">
         <v>0</v>
@@ -7224,46 +7212,46 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM14" t="n">
         <v>1</v>
       </c>
       <c r="CN14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
         <v>0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ14" t="n">
         <v>1</v>
       </c>
       <c r="CR14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CS14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CT14" t="n">
         <v>1</v>
       </c>
       <c r="CU14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CV14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="CW14" t="n">
         <v>1</v>
       </c>
       <c r="CX14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="CY14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ14" t="n">
         <v>0</v>
@@ -7281,7 +7269,7 @@
         <v>3</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7332,64 +7320,76 @@
         <v>0</v>
       </c>
       <c r="DV14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="DX14" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="DY14" t="inlineStr">
         <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="DZ14" t="inlineStr"/>
-      <c r="EA14" t="inlineStr"/>
-      <c r="EB14" t="inlineStr"/>
+          <t>5.58</t>
+        </is>
+      </c>
+      <c r="DZ14" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EA14" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EB14" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
       <c r="EC14" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="ED14" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EE14" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EF14" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EG14" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EH14" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EI14" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="EF14" t="inlineStr">
+      <c r="EJ14" t="inlineStr">
         <is>
           <t>2.34</t>
-        </is>
-      </c>
-      <c r="EG14" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EH14" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EI14" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EJ14" t="inlineStr">
-        <is>
-          <t>2.33</t>
         </is>
       </c>
       <c r="EK14" t="inlineStr"/>
@@ -7820,32 +7820,32 @@
       </c>
       <c r="EE15" t="inlineStr">
         <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EF15" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EG15" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EH15" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EI15" t="inlineStr">
+        <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="EF15" t="inlineStr">
+      <c r="EJ15" t="inlineStr">
         <is>
           <t>2.62</t>
-        </is>
-      </c>
-      <c r="EG15" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EH15" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EI15" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EJ15" t="inlineStr">
-        <is>
-          <t>2.22</t>
         </is>
       </c>
       <c r="EK15" t="inlineStr">
@@ -8292,26 +8292,26 @@
       </c>
       <c r="EE16" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EF16" t="inlineStr"/>
+      <c r="EG16" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EH16" t="inlineStr"/>
+      <c r="EI16" t="inlineStr">
+        <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="EF16" t="inlineStr">
+      <c r="EJ16" t="inlineStr">
         <is>
           <t>2.17</t>
         </is>
       </c>
-      <c r="EG16" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EH16" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="EI16" t="inlineStr"/>
-      <c r="EJ16" t="inlineStr"/>
       <c r="EK16" t="inlineStr"/>
       <c r="EL16" t="inlineStr"/>
     </row>
@@ -8748,32 +8748,32 @@
       </c>
       <c r="EE17" t="inlineStr">
         <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EF17" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EG17" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EH17" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EI17" t="inlineStr">
+        <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="EF17" t="inlineStr">
+      <c r="EJ17" t="inlineStr">
         <is>
           <t>2.54</t>
-        </is>
-      </c>
-      <c r="EG17" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EH17" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EI17" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EJ17" t="inlineStr">
-        <is>
-          <t>2.33</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr"/>
@@ -9204,32 +9204,32 @@
       </c>
       <c r="EE18" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EF18" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EG18" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EH18" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EI18" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="EF18" t="inlineStr">
+      <c r="EJ18" t="inlineStr">
         <is>
           <t>2.40</t>
-        </is>
-      </c>
-      <c r="EG18" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EH18" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="EI18" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EJ18" t="inlineStr">
-        <is>
-          <t>2.37</t>
         </is>
       </c>
       <c r="EK18" t="inlineStr"/>
@@ -9658,18 +9658,18 @@
           <t>2.64</t>
         </is>
       </c>
-      <c r="EE19" t="inlineStr"/>
+      <c r="EE19" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
       <c r="EF19" t="inlineStr"/>
       <c r="EG19" t="inlineStr">
         <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="EH19" t="inlineStr">
-        <is>
           <t>2.11</t>
         </is>
       </c>
+      <c r="EH19" t="inlineStr"/>
       <c r="EI19" t="inlineStr"/>
       <c r="EJ19" t="inlineStr"/>
       <c r="EK19" t="inlineStr"/>
@@ -10960,26 +10960,26 @@
       </c>
       <c r="EE22" t="inlineStr">
         <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EF22" t="inlineStr"/>
+      <c r="EG22" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EH22" t="inlineStr"/>
+      <c r="EI22" t="inlineStr">
+        <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="EF22" t="inlineStr">
+      <c r="EJ22" t="inlineStr">
         <is>
           <t>2.60</t>
         </is>
       </c>
-      <c r="EG22" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EH22" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EI22" t="inlineStr"/>
-      <c r="EJ22" t="inlineStr"/>
       <c r="EK22" t="inlineStr"/>
       <c r="EL22" t="inlineStr"/>
     </row>
@@ -11416,32 +11416,32 @@
       </c>
       <c r="EE23" t="inlineStr">
         <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EF23" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EG23" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH23" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EI23" t="inlineStr">
+        <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="EF23" t="inlineStr">
+      <c r="EJ23" t="inlineStr">
         <is>
           <t>2.58</t>
-        </is>
-      </c>
-      <c r="EG23" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EH23" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EI23" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EJ23" t="inlineStr">
-        <is>
-          <t>2.40</t>
         </is>
       </c>
       <c r="EK23" t="inlineStr">
@@ -11886,28 +11886,28 @@
           <t>2.35</t>
         </is>
       </c>
-      <c r="EE24" t="inlineStr"/>
-      <c r="EF24" t="inlineStr"/>
+      <c r="EE24" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EF24" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
       <c r="EG24" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EH24" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EI24" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EJ24" t="inlineStr">
-        <is>
           <t>2.30</t>
         </is>
       </c>
+      <c r="EI24" t="inlineStr"/>
+      <c r="EJ24" t="inlineStr"/>
       <c r="EK24" t="inlineStr"/>
       <c r="EL24" t="inlineStr"/>
     </row>
@@ -12342,28 +12342,28 @@
           <t>2.77</t>
         </is>
       </c>
-      <c r="EE25" t="inlineStr"/>
-      <c r="EF25" t="inlineStr"/>
+      <c r="EE25" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EF25" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
       <c r="EG25" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EH25" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EI25" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EJ25" t="inlineStr">
-        <is>
           <t>2.25</t>
         </is>
       </c>
+      <c r="EI25" t="inlineStr"/>
+      <c r="EJ25" t="inlineStr"/>
       <c r="EK25" t="inlineStr"/>
       <c r="EL25" t="inlineStr"/>
     </row>
@@ -12800,32 +12800,32 @@
       </c>
       <c r="EE26" t="inlineStr">
         <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EF26" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EG26" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EH26" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EI26" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="EF26" t="inlineStr">
+      <c r="EJ26" t="inlineStr">
         <is>
           <t>2.39</t>
-        </is>
-      </c>
-      <c r="EG26" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="EH26" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="EI26" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EJ26" t="inlineStr">
-        <is>
-          <t>2.49</t>
         </is>
       </c>
       <c r="EK26" t="inlineStr"/>
@@ -13254,18 +13254,18 @@
           <t>2.45</t>
         </is>
       </c>
-      <c r="EE27" t="inlineStr"/>
+      <c r="EE27" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
       <c r="EF27" t="inlineStr"/>
       <c r="EG27" t="inlineStr">
         <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EH27" t="inlineStr">
-        <is>
           <t>2.04</t>
         </is>
       </c>
+      <c r="EH27" t="inlineStr"/>
       <c r="EI27" t="inlineStr"/>
       <c r="EJ27" t="inlineStr"/>
       <c r="EK27" t="inlineStr"/>
@@ -13694,28 +13694,28 @@
           <t>2.02</t>
         </is>
       </c>
-      <c r="EE28" t="inlineStr"/>
-      <c r="EF28" t="inlineStr"/>
+      <c r="EE28" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EF28" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
       <c r="EG28" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EH28" t="inlineStr">
         <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EI28" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EJ28" t="inlineStr">
-        <is>
           <t>2.58</t>
         </is>
       </c>
+      <c r="EI28" t="inlineStr"/>
+      <c r="EJ28" t="inlineStr"/>
       <c r="EK28" t="inlineStr"/>
       <c r="EL28" t="inlineStr"/>
     </row>
@@ -14142,28 +14142,28 @@
           <t>2.08</t>
         </is>
       </c>
-      <c r="EE29" t="inlineStr"/>
-      <c r="EF29" t="inlineStr"/>
+      <c r="EE29" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF29" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
       <c r="EG29" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EH29" t="inlineStr">
         <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EI29" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EJ29" t="inlineStr">
-        <is>
           <t>2.52</t>
         </is>
       </c>
+      <c r="EI29" t="inlineStr"/>
+      <c r="EJ29" t="inlineStr"/>
       <c r="EK29" t="inlineStr"/>
       <c r="EL29" t="inlineStr"/>
     </row>
@@ -14592,32 +14592,32 @@
       </c>
       <c r="EE30" t="inlineStr">
         <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EF30" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EG30" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH30" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EI30" t="inlineStr">
+        <is>
           <t>1.87</t>
         </is>
       </c>
-      <c r="EF30" t="inlineStr">
+      <c r="EJ30" t="inlineStr">
         <is>
           <t>2.00</t>
-        </is>
-      </c>
-      <c r="EG30" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EH30" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EI30" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EJ30" t="inlineStr">
-        <is>
-          <t>2.34</t>
         </is>
       </c>
       <c r="EK30" t="inlineStr"/>
@@ -15048,36 +15048,492 @@
       </c>
       <c r="EE31" t="inlineStr">
         <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EF31" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EG31" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH31" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EI31" t="inlineStr">
+        <is>
           <t>1.70</t>
         </is>
       </c>
-      <c r="EF31" t="inlineStr">
+      <c r="EJ31" t="inlineStr">
         <is>
           <t>2.22</t>
-        </is>
-      </c>
-      <c r="EG31" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EH31" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EI31" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EJ31" t="inlineStr">
-        <is>
-          <t>2.44</t>
         </is>
       </c>
       <c r="EK31" t="inlineStr"/>
       <c r="EL31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>USA_Major_League_Soccer_2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>46088.8125</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>13</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4</v>
+      </c>
+      <c r="W32" t="n">
+        <v>9</v>
+      </c>
+      <c r="X32" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Yankee Stadium</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>One East 161st Street, The Bronx, New York City</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>14</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>41</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="CB32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR32" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS32" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU32" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV32" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX32" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY32" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD32" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH32" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO32" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP32" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ32" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR32" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS32" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT32" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU32" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV32" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW32" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="DX32" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="DY32" t="inlineStr">
+        <is>
+          <t>4.74</t>
+        </is>
+      </c>
+      <c r="DZ32" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EA32" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EB32" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EC32" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="ED32" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EE32" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EF32" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EG32" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EH32" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EI32" t="inlineStr"/>
+      <c r="EJ32" t="inlineStr"/>
+      <c r="EK32" t="inlineStr"/>
+      <c r="EL32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -16616,7 +16616,7 @@
         <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>-1</v>
+        <v>53862</v>
       </c>
       <c r="BG35" t="n">
         <v>2</v>
@@ -17080,7 +17080,7 @@
         <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>-1</v>
+        <v>20121</v>
       </c>
       <c r="BG36" t="n">
         <v>2</v>
@@ -17536,7 +17536,7 @@
         <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>-1</v>
+        <v>35611</v>
       </c>
       <c r="BG37" t="n">
         <v>2</v>
@@ -19332,7 +19332,7 @@
         <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>-1</v>
+        <v>14568</v>
       </c>
       <c r="BG41" t="n">
         <v>2</v>
@@ -19776,7 +19776,7 @@
         <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>-1</v>
+        <v>22130</v>
       </c>
       <c r="BG42" t="n">
         <v>2</v>
@@ -20220,7 +20220,7 @@
         <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>-1</v>
+        <v>22473</v>
       </c>
       <c r="BG43" t="n">
         <v>2</v>

--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -21564,7 +21564,7 @@
         <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>-1</v>
+        <v>18767</v>
       </c>
       <c r="BG46" t="n">
         <v>2</v>
@@ -21915,13 +21915,13 @@
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T47" t="n">
         <v>11</v>
       </c>
       <c r="U47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V47" t="n">
         <v>14</v>
@@ -22096,13 +22096,13 @@
         <v>141</v>
       </c>
       <c r="BZ47" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="CA47" t="n">
         <v>1.78</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="CC47" t="n">
         <v>0</v>
@@ -22508,7 +22508,7 @@
         <v>0</v>
       </c>
       <c r="BF48" t="n">
-        <v>-1</v>
+        <v>19960</v>
       </c>
       <c r="BG48" t="n">
         <v>-1</v>
@@ -22964,7 +22964,7 @@
         <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>-1</v>
+        <v>18079</v>
       </c>
       <c r="BG49" t="n">
         <v>2</v>
@@ -23081,7 +23081,7 @@
         <v>16</v>
       </c>
       <c r="CS49" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CT49" t="n">
         <v>1</v>
@@ -23090,7 +23090,7 @@
         <v>25</v>
       </c>
       <c r="CV49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CW49" t="n">
         <v>1</v>
@@ -23412,7 +23412,7 @@
         <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>-1</v>
+        <v>34780</v>
       </c>
       <c r="BG50" t="n">
         <v>2</v>
@@ -23744,13 +23744,13 @@
         <v>6</v>
       </c>
       <c r="R51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
       </c>
       <c r="T51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U51" t="n">
         <v>15</v>
@@ -23762,7 +23762,7 @@
         <v>12</v>
       </c>
       <c r="X51" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y51" t="n">
         <v>35</v>
@@ -23923,10 +23923,10 @@
         <v>1.41</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="CB51" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="CC51" t="n">
         <v>0</v>
@@ -23983,7 +23983,7 @@
         <v>1</v>
       </c>
       <c r="CU51" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CV51" t="n">
         <v>12</v>
@@ -24663,16 +24663,16 @@
         <v>13</v>
       </c>
       <c r="W53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X53" t="n">
         <v>11</v>
       </c>
       <c r="Y53" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z53" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
@@ -25228,7 +25228,7 @@
         <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>-1</v>
+        <v>11004</v>
       </c>
       <c r="BG54" t="n">
         <v>2</v>
@@ -26116,7 +26116,7 @@
         <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>-1</v>
+        <v>18232</v>
       </c>
       <c r="BG56" t="n">
         <v>2</v>
@@ -26580,7 +26580,7 @@
         <v>0</v>
       </c>
       <c r="BF57" t="n">
-        <v>-1</v>
+        <v>22266</v>
       </c>
       <c r="BG57" t="n">
         <v>2</v>
@@ -26893,34 +26893,34 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R58" t="n">
         <v>9</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T58" t="n">
         <v>6</v>
       </c>
       <c r="U58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V58" t="n">
         <v>15</v>
       </c>
       <c r="W58" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X58" t="n">
         <v>14</v>
       </c>
       <c r="Y58" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z58" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>0</v>
       </c>
       <c r="BF58" t="n">
-        <v>-1</v>
+        <v>15627</v>
       </c>
       <c r="BG58" t="n">
         <v>2</v>
@@ -27080,13 +27080,13 @@
         <v>86</v>
       </c>
       <c r="BZ58" t="n">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="CA58" t="n">
         <v>1.84</v>
       </c>
       <c r="CB58" t="n">
-        <v>3.66</v>
+        <v>3.86</v>
       </c>
       <c r="CC58" t="n">
         <v>0</v>
@@ -27137,7 +27137,7 @@
         <v>8</v>
       </c>
       <c r="CS58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CT58" t="n">
         <v>1</v>
@@ -27367,10 +27367,10 @@
         <v>8</v>
       </c>
       <c r="W59" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X59" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y59" t="n">
         <v>50</v>
@@ -27476,7 +27476,7 @@
         <v>0</v>
       </c>
       <c r="BF59" t="n">
-        <v>-1</v>
+        <v>23885</v>
       </c>
       <c r="BG59" t="n">
         <v>2</v>
@@ -27916,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>-1</v>
+        <v>18251</v>
       </c>
       <c r="BG60" t="n">
         <v>-1</v>

--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -27370,7 +27370,7 @@
         <v>23</v>
       </c>
       <c r="X59" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y59" t="n">
         <v>50</v>

--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -28380,7 +28380,7 @@
         <v>0</v>
       </c>
       <c r="BF61" t="n">
-        <v>-1</v>
+        <v>15384</v>
       </c>
       <c r="BG61" t="n">
         <v>2</v>
@@ -28727,10 +28727,10 @@
         <v>11</v>
       </c>
       <c r="W62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X62" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y62" t="n">
         <v>47</v>
@@ -30188,7 +30188,7 @@
         <v>0</v>
       </c>
       <c r="BF65" t="n">
-        <v>-1</v>
+        <v>35418</v>
       </c>
       <c r="BG65" t="n">
         <v>2</v>
@@ -30636,7 +30636,7 @@
         <v>0</v>
       </c>
       <c r="BF66" t="n">
-        <v>-1</v>
+        <v>17037</v>
       </c>
       <c r="BG66" t="n">
         <v>2</v>
@@ -31084,7 +31084,7 @@
         <v>0</v>
       </c>
       <c r="BF67" t="n">
-        <v>-1</v>
+        <v>22423</v>
       </c>
       <c r="BG67" t="n">
         <v>2</v>
@@ -31548,7 +31548,7 @@
         <v>0</v>
       </c>
       <c r="BF68" t="n">
-        <v>-1</v>
+        <v>11004</v>
       </c>
       <c r="BG68" t="n">
         <v>2</v>
@@ -32782,7 +32782,7 @@
         <v>12</v>
       </c>
       <c r="X71" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y71" t="n">
         <v>46</v>
@@ -32888,7 +32888,7 @@
         <v>0</v>
       </c>
       <c r="BF71" t="n">
-        <v>-1</v>
+        <v>45845</v>
       </c>
       <c r="BG71" t="n">
         <v>2</v>
@@ -33235,16 +33235,16 @@
         <v>19</v>
       </c>
       <c r="W72" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="X72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y72" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z72" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
@@ -33336,7 +33336,7 @@
         <v>0</v>
       </c>
       <c r="BF72" t="n">
-        <v>-1</v>
+        <v>25513</v>
       </c>
       <c r="BG72" t="n">
         <v>2</v>
@@ -33683,7 +33683,7 @@
         <v>11</v>
       </c>
       <c r="W73" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X73" t="n">
         <v>13</v>
@@ -33784,7 +33784,7 @@
         <v>0</v>
       </c>
       <c r="BF73" t="n">
-        <v>-1</v>
+        <v>19637</v>
       </c>
       <c r="BG73" t="n">
         <v>2</v>
@@ -34142,7 +34142,7 @@
         <v>11</v>
       </c>
       <c r="X74" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y74" t="n">
         <v>34</v>
@@ -34569,7 +34569,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R75" t="n">
         <v>8</v>
@@ -34581,22 +34581,22 @@
         <v>13</v>
       </c>
       <c r="U75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V75" t="n">
         <v>21</v>
       </c>
       <c r="W75" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="X75" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y75" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z75" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr"/>
@@ -34688,7 +34688,7 @@
         <v>0</v>
       </c>
       <c r="BF75" t="n">
-        <v>-1</v>
+        <v>24141</v>
       </c>
       <c r="BG75" t="n">
         <v>2</v>
@@ -34748,13 +34748,13 @@
         <v>70</v>
       </c>
       <c r="BZ75" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="CA75" t="n">
         <v>1.98</v>
       </c>
       <c r="CB75" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="CC75" t="n">
         <v>0</v>

--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -32782,7 +32782,7 @@
         <v>12</v>
       </c>
       <c r="X71" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y71" t="n">
         <v>46</v>
@@ -33235,10 +33235,10 @@
         <v>19</v>
       </c>
       <c r="W72" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="X72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y72" t="n">
         <v>46</v>

--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -2381,10 +2381,10 @@
         <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>12</v>
       </c>
       <c r="W4" t="n">
+        <v>19</v>
+      </c>
+      <c r="X4" t="n">
         <v>16</v>
-      </c>
-      <c r="X4" t="n">
-        <v>12</v>
       </c>
       <c r="Y4" t="n">
         <v>49</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
         <v>3.28</v>
@@ -2553,16 +2553,16 @@
         <v>2</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS4" t="n">
         <v>2</v>
       </c>
       <c r="BT4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU4" t="n">
         <v>1</v>
@@ -7572,7 +7572,7 @@
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-1</v>
+        <v>25025</v>
       </c>
       <c r="BG15" t="n">
         <v>2</v>
@@ -10292,7 +10292,7 @@
         <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>-1</v>
+        <v>20660</v>
       </c>
       <c r="BG21" t="n">
         <v>2</v>
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>-1</v>
+        <v>16159</v>
       </c>
       <c r="BG22" t="n">
         <v>2</v>
@@ -11171,28 +11171,28 @@
         <v>-1</v>
       </c>
       <c r="BG23" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH23" t="n">
         <v>1</v>
       </c>
       <c r="BI23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BJ23" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BK23" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BL23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BM23" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BN23" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BO23" t="n">
         <v>0</v>
@@ -11267,10 +11267,10 @@
         <v>0</v>
       </c>
       <c r="CM23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CO23" t="n">
         <v>0</v>
@@ -11624,7 +11624,7 @@
         <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>-1</v>
+        <v>18522</v>
       </c>
       <c r="BG24" t="n">
         <v>2</v>
@@ -13008,7 +13008,7 @@
         <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>-1</v>
+        <v>20205</v>
       </c>
       <c r="BG27" t="n">
         <v>2</v>
@@ -15155,7 +15155,7 @@
         <v>4</v>
       </c>
       <c r="W32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X32" t="n">
         <v>7</v>
@@ -17080,7 +17080,7 @@
         <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>-1</v>
+        <v>17410</v>
       </c>
       <c r="BG36" t="n">
         <v>2</v>
@@ -17992,7 +17992,7 @@
         <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>-1</v>
+        <v>14294</v>
       </c>
       <c r="BG38" t="n">
         <v>2</v>
@@ -18420,7 +18420,7 @@
         <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>-1</v>
+        <v>24387</v>
       </c>
       <c r="BG39" t="n">
         <v>2</v>
@@ -18884,7 +18884,7 @@
         <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>-1</v>
+        <v>22423</v>
       </c>
       <c r="BG40" t="n">
         <v>2</v>
@@ -23306,7 +23306,7 @@
         <v>12</v>
       </c>
       <c r="X50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y50" t="n">
         <v>35</v>
@@ -24756,7 +24756,7 @@
         <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>-1</v>
+        <v>15845</v>
       </c>
       <c r="BG53" t="n">
         <v>2</v>
@@ -25220,7 +25220,7 @@
         <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>-1</v>
+        <v>18026</v>
       </c>
       <c r="BG54" t="n">
         <v>2</v>
@@ -25352,7 +25352,7 @@
         <v>1</v>
       </c>
       <c r="CX54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CY54" t="n">
         <v>8</v>
@@ -25676,7 +25676,7 @@
         <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>-1</v>
+        <v>20751</v>
       </c>
       <c r="BG55" t="n">
         <v>2</v>
@@ -27370,7 +27370,7 @@
         <v>23</v>
       </c>
       <c r="X59" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y59" t="n">
         <v>50</v>
@@ -28727,10 +28727,10 @@
         <v>11</v>
       </c>
       <c r="W62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X62" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y62" t="n">
         <v>47</v>
@@ -31988,7 +31988,7 @@
         <v>0</v>
       </c>
       <c r="BF69" t="n">
-        <v>-1</v>
+        <v>20738</v>
       </c>
       <c r="BG69" t="n">
         <v>2</v>
@@ -32452,7 +32452,7 @@
         <v>0</v>
       </c>
       <c r="BF70" t="n">
-        <v>-1</v>
+        <v>21261</v>
       </c>
       <c r="BG70" t="n">
         <v>2</v>
@@ -32752,7 +32752,7 @@
         <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -32804,7 +32804,7 @@
         <v>1</v>
       </c>
       <c r="AD71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE71" t="n">
         <v>2.35</v>
@@ -32924,13 +32924,13 @@
         <v>1</v>
       </c>
       <c r="BR71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS71" t="n">
         <v>1</v>
       </c>
       <c r="BT71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU71" t="n">
         <v>1</v>

--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -35258,10 +35258,10 @@
         <v>1</v>
       </c>
       <c r="CR76" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CS76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CT76" t="n">
         <v>1</v>
@@ -35600,7 +35600,7 @@
         <v>0</v>
       </c>
       <c r="BF77" t="n">
-        <v>-1</v>
+        <v>20290</v>
       </c>
       <c r="BG77" t="n">
         <v>2</v>
@@ -36040,7 +36040,7 @@
         <v>0</v>
       </c>
       <c r="BF78" t="n">
-        <v>-1</v>
+        <v>19461</v>
       </c>
       <c r="BG78" t="n">
         <v>2</v>
@@ -36383,13 +36383,13 @@
         <v>3</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T79" t="n">
         <v>11</v>
       </c>
       <c r="U79" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V79" t="n">
         <v>14</v>
@@ -36401,10 +36401,10 @@
         <v>12</v>
       </c>
       <c r="Y79" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="Z79" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AA79" t="inlineStr"/>
       <c r="AB79" t="inlineStr"/>
@@ -36496,31 +36496,31 @@
         <v>0</v>
       </c>
       <c r="BF79" t="n">
-        <v>-1</v>
+        <v>20867</v>
       </c>
       <c r="BG79" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH79" t="n">
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BJ79" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BK79" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL79" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BM79" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BN79" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BO79" t="n">
         <v>0</v>
@@ -36556,13 +36556,13 @@
         <v>97</v>
       </c>
       <c r="BZ79" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="CA79" t="n">
         <v>1.41</v>
       </c>
       <c r="CB79" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="CC79" t="n">
         <v>0</v>
@@ -36595,10 +36595,10 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN79" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CO79" t="n">
         <v>0</v>
@@ -36610,19 +36610,19 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="CS79" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
       </c>
       <c r="CU79" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="CV79" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="CW79" t="n">
         <v>1</v>
@@ -36631,7 +36631,7 @@
         <v>8</v>
       </c>
       <c r="CY79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CZ79" t="n">
         <v>50</v>
@@ -36788,7 +36788,7 @@
         <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -36840,7 +36840,7 @@
         <v>1</v>
       </c>
       <c r="AD80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
         <v>2.88</v>
@@ -36924,7 +36924,7 @@
         <v>0</v>
       </c>
       <c r="BF80" t="n">
-        <v>-1</v>
+        <v>34130</v>
       </c>
       <c r="BG80" t="n">
         <v>2</v>
@@ -36960,13 +36960,13 @@
         <v>1</v>
       </c>
       <c r="BR80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS80" t="n">
         <v>0</v>
       </c>
       <c r="BT80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU80" t="n">
         <v>1</v>
@@ -37259,13 +37259,13 @@
         <v>3</v>
       </c>
       <c r="S81" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T81" t="n">
         <v>6</v>
       </c>
       <c r="U81" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V81" t="n">
         <v>9</v>
@@ -37372,7 +37372,7 @@
         <v>0</v>
       </c>
       <c r="BF81" t="n">
-        <v>-1</v>
+        <v>26412</v>
       </c>
       <c r="BG81" t="n">
         <v>2</v>
@@ -37432,13 +37432,13 @@
         <v>56</v>
       </c>
       <c r="BZ81" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="CA81" t="n">
         <v>0.96</v>
       </c>
       <c r="CB81" t="n">
-        <v>3.75</v>
+        <v>3.81</v>
       </c>
       <c r="CC81" t="n">
         <v>0</v>
@@ -37828,7 +37828,7 @@
         <v>0</v>
       </c>
       <c r="BF82" t="n">
-        <v>-1</v>
+        <v>19215</v>
       </c>
       <c r="BG82" t="n">
         <v>2</v>
@@ -38178,7 +38178,7 @@
         <v>12</v>
       </c>
       <c r="X83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y83" t="n">
         <v>52</v>
@@ -38284,7 +38284,7 @@
         <v>0</v>
       </c>
       <c r="BF83" t="n">
-        <v>-1</v>
+        <v>20867</v>
       </c>
       <c r="BG83" t="n">
         <v>2</v>
@@ -38407,7 +38407,7 @@
         <v>1</v>
       </c>
       <c r="CU83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CV83" t="n">
         <v>12</v>
@@ -38629,10 +38629,10 @@
         <v>22</v>
       </c>
       <c r="Y84" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="Z84" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr"/>
@@ -38724,7 +38724,7 @@
         <v>0</v>
       </c>
       <c r="BF84" t="n">
-        <v>-1</v>
+        <v>25865</v>
       </c>
       <c r="BG84" t="n">
         <v>2</v>
@@ -38838,19 +38838,19 @@
         <v>1</v>
       </c>
       <c r="CR84" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="CS84" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="CT84" t="n">
         <v>1</v>
       </c>
       <c r="CU84" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="CV84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="CW84" t="n">
         <v>1</v>
@@ -39062,13 +39062,13 @@
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U85" t="n">
         <v>10</v>
       </c>
       <c r="V85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W85" t="n">
         <v>19</v>
@@ -39172,7 +39172,7 @@
         <v>0</v>
       </c>
       <c r="BF85" t="n">
-        <v>-1</v>
+        <v>15932</v>
       </c>
       <c r="BG85" t="n">
         <v>2</v>
@@ -39235,10 +39235,10 @@
         <v>0.99</v>
       </c>
       <c r="CA85" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="CB85" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="CC85" t="n">
         <v>0</v>
@@ -39530,7 +39530,7 @@
         <v>5</v>
       </c>
       <c r="X86" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y86" t="n">
         <v>45</v>
@@ -39636,7 +39636,7 @@
         <v>0</v>
       </c>
       <c r="BF86" t="n">
-        <v>-1</v>
+        <v>17253</v>
       </c>
       <c r="BG86" t="n">
         <v>2</v>
@@ -39759,7 +39759,7 @@
         <v>1</v>
       </c>
       <c r="CU86" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV86" t="n">
         <v>5</v>
@@ -40076,7 +40076,7 @@
         <v>0</v>
       </c>
       <c r="BF87" t="n">
-        <v>-1</v>
+        <v>22185</v>
       </c>
       <c r="BG87" t="n">
         <v>2</v>
@@ -40508,7 +40508,7 @@
         <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>-1</v>
+        <v>22447</v>
       </c>
       <c r="BG88" t="n">
         <v>-1</v>
@@ -40940,7 +40940,7 @@
         <v>0</v>
       </c>
       <c r="BF89" t="n">
-        <v>-1</v>
+        <v>18251</v>
       </c>
       <c r="BG89" t="n">
         <v>2</v>
@@ -41368,7 +41368,7 @@
         <v>0</v>
       </c>
       <c r="BF90" t="n">
-        <v>-1</v>
+        <v>25465</v>
       </c>
       <c r="BG90" t="n">
         <v>2</v>

--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -39973,10 +39973,10 @@
         <v>14</v>
       </c>
       <c r="Y87" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Z87" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>

--- a/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
+++ b/data/matches/leagues/USA_Major_League_Soccer_2026.xlsx
@@ -597,8 +597,8 @@
     <col width="16.8" customWidth="1" min="24" max="24"/>
     <col width="22.8" customWidth="1" min="25" max="25"/>
     <col width="22.8" customWidth="1" min="26" max="26"/>
-    <col width="33.6" customWidth="1" min="27" max="27"/>
-    <col width="50" customWidth="1" min="28" max="28"/>
+    <col width="16.8" customWidth="1" min="27" max="27"/>
+    <col width="21.6" customWidth="1" min="28" max="28"/>
     <col width="21.6" customWidth="1" min="29" max="29"/>
     <col width="21.6" customWidth="1" min="30" max="30"/>
     <col width="18" customWidth="1" min="31" max="31"/>
@@ -2874,16 +2874,8 @@
       <c r="Z5" t="n">
         <v>41</v>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>BC Place Stadium</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>777 Pacific Boulevard, False Creek, Vancouver, British Columbia</t>
-        </is>
-      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
         <v>2</v>
       </c>
@@ -3330,16 +3322,8 @@
       <c r="Z6" t="n">
         <v>51</v>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Audi Field</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>32-60 R Street South West, Buzzard Point, Washington, District of Columbia</t>
-        </is>
-      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
         <v>2</v>
       </c>
@@ -4258,16 +4242,8 @@
       <c r="Z8" t="n">
         <v>55</v>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Toyota Stadium</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>6000 Main Street, Frisco, Texas</t>
-        </is>
-      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
         <v>1</v>
       </c>
@@ -4730,16 +4706,8 @@
       <c r="Z9" t="n">
         <v>57</v>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>BBVA Compass Stadium</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>2200 Texas Avenue, East End, Houston, Texas</t>
-        </is>
-      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
         <v>3</v>
       </c>
@@ -7018,16 +6986,8 @@
       <c r="Z14" t="n">
         <v>54</v>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Providence Park</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>1844 SW Morrison Street, Portland, Oregon</t>
-        </is>
-      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
         <v>1</v>
       </c>
@@ -7934,16 +7894,8 @@
       <c r="Z16" t="n">
         <v>57</v>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>CenturyLink Field</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>800 Occidental Avenue South, Seattle, Washington</t>
-        </is>
-      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
         <v>2</v>
       </c>
@@ -8390,16 +8342,8 @@
       <c r="Z17" t="n">
         <v>35</v>
       </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Red Bull Arena</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Frank Rogers Boulevard South, Harrison, New Jersey</t>
-        </is>
-      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
         <v>2</v>
       </c>
@@ -10618,16 +10562,8 @@
       <c r="Z22" t="n">
         <v>61</v>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Rio Tinto Stadium</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>9256 South State Street, Sandy, Utah</t>
-        </is>
-      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
         <v>3</v>
       </c>
@@ -11058,16 +10994,8 @@
       <c r="Z23" t="n">
         <v>53</v>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Toyota Stadium</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>6000 Main Street, Frisco, Texas</t>
-        </is>
-      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
         <v>3</v>
       </c>
@@ -11514,16 +11442,8 @@
       <c r="Z24" t="n">
         <v>58</v>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Children's Mercy Park</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>One Sporting Way, Kansas City, Kansas</t>
-        </is>
-      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
         <v>1</v>
       </c>
@@ -11970,16 +11890,8 @@
       <c r="Z25" t="n">
         <v>71</v>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>BBVA Compass Stadium</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>2200 Texas Avenue, East End, Houston, Texas</t>
-        </is>
-      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
         <v>5</v>
       </c>
@@ -12442,16 +12354,8 @@
       <c r="Z26" t="n">
         <v>40</v>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>BC Place Stadium</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>777 Pacific Boulevard, False Creek, Vancouver, British Columbia</t>
-        </is>
-      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
         <v>1</v>
       </c>
@@ -15154,16 +15058,8 @@
       <c r="Z32" t="n">
         <v>28</v>
       </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Yankee Stadium</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>One East 161st Street, The Bronx, New York City</t>
-        </is>
-      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
@@ -15610,16 +15506,8 @@
       <c r="Z33" t="n">
         <v>64</v>
       </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Audi Field</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>32-60 R Street South West, Buzzard Point, Washington, District of Columbia</t>
-        </is>
-      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
         <v>1</v>
       </c>
@@ -16506,16 +16394,8 @@
       <c r="Z35" t="n">
         <v>38</v>
       </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz Stadium</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>1 AMB Drive North West, Atlanta, Georgia</t>
-        </is>
-      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
         <v>2</v>
       </c>
@@ -16970,16 +16850,8 @@
       <c r="Z36" t="n">
         <v>49</v>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>MAPFRE Stadium</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>1 Black and Gold Boulevard, Columbus, Ohio</t>
-        </is>
-      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
         <v>2</v>
       </c>
@@ -18330,16 +18202,8 @@
       <c r="Z39" t="n">
         <v>67</v>
       </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>Children's Mercy Park</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>One Sporting Way, Kansas City, Kansas</t>
-        </is>
-      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
         <v>3</v>
       </c>
@@ -19666,16 +19530,8 @@
       <c r="Z42" t="n">
         <v>55</v>
       </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>Providence Park</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>1844 SW Morrison Street, Portland, Oregon</t>
-        </is>
-      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
         <v>3</v>
       </c>
@@ -20114,16 +19970,8 @@
       <c r="Z43" t="n">
         <v>39</v>
       </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Banc of California Stadium</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>3939 S Figueroa Street, Los Angeles, California</t>
-        </is>
-      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
         <v>2</v>
       </c>
@@ -20558,16 +20406,8 @@
       <c r="Z44" t="n">
         <v>33</v>
       </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>Red Bull Arena</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>Frank Rogers Boulevard South, Harrison, New Jersey</t>
-        </is>
-      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
         <v>1</v>
       </c>
@@ -21926,16 +21766,8 @@
       <c r="Z47" t="n">
         <v>58</v>
       </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz Stadium</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>1 AMB Drive North West, Atlanta, Georgia</t>
-        </is>
-      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
         <v>4</v>
       </c>
@@ -22398,16 +22230,8 @@
       <c r="Z48" t="n">
         <v>43</v>
       </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>MAPFRE Stadium</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>1 Black and Gold Boulevard, Columbus, Ohio</t>
-        </is>
-      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
         <v>1</v>
       </c>
@@ -22854,16 +22678,8 @@
       <c r="Z49" t="n">
         <v>59</v>
       </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>Yankee Stadium</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>One East 161st Street, The Bronx, New York City</t>
-        </is>
-      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
         <v>2</v>
       </c>
@@ -24662,16 +24478,8 @@
       <c r="Z53" t="n">
         <v>65</v>
       </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>Toyota Stadium</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>6000 Main Street, Frisco, Texas</t>
-        </is>
-      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
         <v>3</v>
       </c>
@@ -25110,16 +24918,8 @@
       <c r="Z54" t="n">
         <v>52</v>
       </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>BBVA Compass Stadium</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>2200 Texas Avenue, East End, Houston, Texas</t>
-        </is>
-      </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
         <v>4</v>
       </c>
@@ -26022,16 +25822,8 @@
       <c r="Z56" t="n">
         <v>40</v>
       </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>Rio Tinto Stadium</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>9256 South State Street, Sandy, Utah</t>
-        </is>
-      </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
         <v>1</v>
       </c>
@@ -26470,16 +26262,8 @@
       <c r="Z57" t="n">
         <v>55</v>
       </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>Banc of California Stadium</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>3939 S Figueroa Street, Los Angeles, California</t>
-        </is>
-      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
         <v>0</v>
       </c>
@@ -26910,16 +26694,8 @@
       <c r="Z58" t="n">
         <v>45</v>
       </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>Gillette Stadium</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>1388 One Patriot Place, Foxborough, Massachusetts</t>
-        </is>
-      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
         <v>3</v>
       </c>
@@ -27366,16 +27142,8 @@
       <c r="Z59" t="n">
         <v>50</v>
       </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>BC Place Stadium</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>777 Pacific Boulevard, False Creek, Vancouver, British Columbia</t>
-        </is>
-      </c>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
         <v>1</v>
       </c>
@@ -29622,16 +29390,8 @@
       <c r="Z64" t="n">
         <v>29</v>
       </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz Stadium</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>1 AMB Drive North West, Atlanta, Georgia</t>
-        </is>
-      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
         <v>1</v>
       </c>
@@ -30982,16 +30742,8 @@
       <c r="Z67" t="n">
         <v>45</v>
       </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>Toyota Stadium</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>6000 Main Street, Frisco, Texas</t>
-        </is>
-      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
         <v>2</v>
       </c>
@@ -31430,16 +31182,8 @@
       <c r="Z68" t="n">
         <v>50</v>
       </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>Children's Mercy Park</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>One Sporting Way, Kansas City, Kansas</t>
-        </is>
-      </c>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
         <v>3</v>
       </c>
@@ -32342,16 +32086,8 @@
       <c r="Z70" t="n">
         <v>39</v>
       </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>BC Place Stadium</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>777 Pacific Boulevard, False Creek, Vancouver, British Columbia</t>
-        </is>
-      </c>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
         <v>1</v>
       </c>
@@ -32778,16 +32514,8 @@
       <c r="Z71" t="n">
         <v>54</v>
       </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>Yankee Stadium</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>One East 161st Street, The Bronx, New York City</t>
-        </is>
-      </c>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
         <v>1</v>
       </c>
@@ -34138,16 +33866,8 @@
       <c r="Z74" t="n">
         <v>66</v>
       </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>Providence Park</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>1844 SW Morrison Street, Portland, Oregon</t>
-        </is>
-      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
         <v>5</v>
       </c>
@@ -35490,16 +35210,8 @@
       <c r="Z77" t="n">
         <v>51</v>
       </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>Rio Tinto Stadium</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>9256 South State Street, Sandy, Utah</t>
-        </is>
-      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
         <v>1</v>
       </c>
@@ -35930,16 +35642,8 @@
       <c r="Z78" t="n">
         <v>64</v>
       </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>Gillette Stadium</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>1388 One Patriot Place, Foxborough, Massachusetts</t>
-        </is>
-      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
         <v>2</v>
       </c>
@@ -36842,16 +36546,8 @@
       <c r="Z80" t="n">
         <v>49</v>
       </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>Audi Field</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>32-60 R Street South West, Buzzard Point, Washington, District of Columbia</t>
-        </is>
-      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
         <v>2</v>
       </c>
@@ -37298,16 +36994,8 @@
       <c r="Z81" t="n">
         <v>42</v>
       </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz Stadium</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>1 AMB Drive North West, Atlanta, Georgia</t>
-        </is>
-      </c>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
         <v>1</v>
       </c>
@@ -38622,16 +38310,8 @@
       <c r="Z84" t="n">
         <v>48</v>
       </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>Red Bull Arena</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>Frank Rogers Boulevard South, Harrison, New Jersey</t>
-        </is>
-      </c>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
         <v>2</v>
       </c>
@@ -39526,16 +39206,8 @@
       <c r="Z86" t="n">
         <v>55</v>
       </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>BBVA Compass Stadium</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>2200 Texas Avenue, East End, Houston, Texas</t>
-        </is>
-      </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
         <v>1</v>
       </c>
@@ -39966,16 +39638,8 @@
       <c r="Z87" t="n">
         <v>56</v>
       </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>Banc of California Stadium</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>3939 S Figueroa Street, Los Angeles, California</t>
-        </is>
-      </c>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
         <v>2</v>
       </c>
@@ -40406,16 +40070,8 @@
       <c r="Z88" t="n">
         <v>39</v>
       </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>BC Place Stadium</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>777 Pacific Boulevard, False Creek, Vancouver, British Columbia</t>
-        </is>
-      </c>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
         <v>1</v>
       </c>
@@ -42586,16 +42242,8 @@
       <c r="Z93" t="n">
         <v>50</v>
       </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>Stade Saputo</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>4750, rue Sherbrooke Est, Montreal, Quebec</t>
-        </is>
-      </c>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="n">
         <v>2</v>
       </c>
@@ -43034,16 +42682,8 @@
       <c r="Z94" t="n">
         <v>42</v>
       </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>Providence Park</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>1844 SW Morrison Street, Portland, Oregon</t>
-        </is>
-      </c>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="n">
         <v>2</v>
       </c>
@@ -44362,16 +44002,8 @@
       <c r="Z97" t="n">
         <v>46</v>
       </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>Gillette Stadium</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>1388 One Patriot Place, Foxborough, Massachusetts</t>
-        </is>
-      </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
         <v>0</v>
       </c>
@@ -44826,16 +44458,8 @@
       <c r="Z98" t="n">
         <v>58</v>
       </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>BC Place Stadium</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>777 Pacific Boulevard, False Creek, Vancouver, British Columbia</t>
-        </is>
-      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="n">
         <v>2</v>
       </c>
@@ -45274,16 +44898,8 @@
       <c r="Z99" t="n">
         <v>51</v>
       </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>Children's Mercy Park</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>One Sporting Way, Kansas City, Kansas</t>
-        </is>
-      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="n">
         <v>2</v>
       </c>
@@ -46134,16 +45750,8 @@
       <c r="Z101" t="n">
         <v>59</v>
       </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>Toyota Stadium</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>6000 Main Street, Frisco, Texas</t>
-        </is>
-      </c>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="n">
         <v>3</v>
       </c>
@@ -47454,16 +47062,8 @@
       <c r="Z104" t="n">
         <v>35</v>
       </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>MAPFRE Stadium</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>1 Black and Gold Boulevard, Columbus, Ohio</t>
-        </is>
-      </c>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="n">
         <v>1</v>
       </c>
@@ -47894,16 +47494,8 @@
       <c r="Z105" t="n">
         <v>50</v>
       </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>BC Place Stadium</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>777 Pacific Boulevard, False Creek, Vancouver, British Columbia</t>
-        </is>
-      </c>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="n">
         <v>1</v>
       </c>
@@ -48778,16 +48370,8 @@
       <c r="Z107" t="n">
         <v>68</v>
       </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>Stade Saputo</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>4750, rue Sherbrooke Est, Montreal, Quebec</t>
-        </is>
-      </c>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="n">
         <v>2</v>
       </c>
@@ -51018,16 +50602,8 @@
       <c r="Z112" t="n">
         <v>52</v>
       </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>Gillette Stadium</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>1388 One Patriot Place, Foxborough, Massachusetts</t>
-        </is>
-      </c>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="n">
         <v>1</v>
       </c>
@@ -51906,16 +51482,8 @@
       <c r="Z114" t="n">
         <v>45</v>
       </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz Stadium</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>1 AMB Drive North West, Atlanta, Georgia</t>
-        </is>
-      </c>
+      <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="n">
         <v>2</v>
       </c>
@@ -52354,16 +51922,8 @@
       <c r="Z115" t="n">
         <v>53</v>
       </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>Toyota Stadium</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>6000 Main Street, Frisco, Texas</t>
-        </is>
-      </c>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="n">
         <v>2</v>
       </c>
@@ -53242,16 +52802,8 @@
       <c r="Z117" t="n">
         <v>50</v>
       </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>CenturyLink Field</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>800 Occidental Avenue South, Seattle, Washington</t>
-        </is>
-      </c>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="n">
         <v>0</v>
       </c>
@@ -53690,16 +53242,8 @@
       <c r="Z118" t="n">
         <v>52</v>
       </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>Rio Tinto Stadium</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>9256 South State Street, Sandy, Utah</t>
-        </is>
-      </c>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="n">
         <v>1</v>
       </c>
@@ -54122,16 +53666,8 @@
       <c r="Z119" t="n">
         <v>47</v>
       </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>Banc of California Stadium</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>3939 S Figueroa Street, Los Angeles, California</t>
-        </is>
-      </c>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="n">
         <v>3</v>
       </c>
@@ -55018,16 +54554,8 @@
       <c r="Z121" t="n">
         <v>45</v>
       </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>Yankee Stadium</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>One East 161st Street, The Bronx, New York City</t>
-        </is>
-      </c>
+      <c r="AA121" t="inlineStr"/>
+      <c r="AB121" t="inlineStr"/>
       <c r="AC121" t="n">
         <v>0</v>
       </c>
@@ -56346,16 +55874,8 @@
       <c r="Z124" t="n">
         <v>52</v>
       </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz Stadium</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>1 AMB Drive North West, Atlanta, Georgia</t>
-        </is>
-      </c>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr"/>
       <c r="AC124" t="n">
         <v>2</v>
       </c>
@@ -56810,16 +56330,8 @@
       <c r="Z125" t="n">
         <v>51</v>
       </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>Toyota Stadium</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>6000 Main Street, Frisco, Texas</t>
-        </is>
-      </c>
+      <c r="AA125" t="inlineStr"/>
+      <c r="AB125" t="inlineStr"/>
       <c r="AC125" t="n">
         <v>2</v>
       </c>
@@ -57258,16 +56770,8 @@
       <c r="Z126" t="n">
         <v>71</v>
       </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>BBVA Compass Stadium</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>2200 Texas Avenue, East End, Houston, Texas</t>
-        </is>
-      </c>
+      <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="n">
         <v>4</v>
       </c>
@@ -57714,16 +57218,8 @@
       <c r="Z127" t="n">
         <v>51</v>
       </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>Rio Tinto Stadium</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>9256 South State Street, Sandy, Utah</t>
-        </is>
-      </c>
+      <c r="AA127" t="inlineStr"/>
+      <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="n">
         <v>3</v>
       </c>
@@ -58154,16 +57650,8 @@
       <c r="Z128" t="n">
         <v>44</v>
       </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>MAPFRE Stadium</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>1 Black and Gold Boulevard, Columbus, Ohio</t>
-        </is>
-      </c>
+      <c r="AA128" t="inlineStr"/>
+      <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="n">
         <v>0</v>
       </c>
@@ -58610,16 +58098,8 @@
       <c r="Z129" t="n">
         <v>73</v>
       </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>Banc of California Stadium</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>3939 S Figueroa Street, Los Angeles, California</t>
-        </is>
-      </c>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="n">
         <v>2</v>
       </c>
@@ -59934,16 +59414,8 @@
       <c r="Z132" t="n">
         <v>65</v>
       </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>Stade Saputo</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>4750, rue Sherbrooke Est, Montreal, Quebec</t>
-        </is>
-      </c>
+      <c r="AA132" t="inlineStr"/>
+      <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="n">
         <v>5</v>
       </c>
@@ -61290,16 +60762,8 @@
       <c r="Z135" t="n">
         <v>44</v>
       </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>MAPFRE Stadium</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>1 Black and Gold Boulevard, Columbus, Ohio</t>
-        </is>
-      </c>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="n">
         <v>1</v>
       </c>
@@ -61754,16 +61218,8 @@
       <c r="Z136" t="n">
         <v>61</v>
       </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>Audi Field</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>32-60 R Street South West, Buzzard Point, Washington, District of Columbia</t>
-        </is>
-      </c>
+      <c r="AA136" t="inlineStr"/>
+      <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="n">
         <v>5</v>
       </c>
@@ -64874,16 +64330,8 @@
       <c r="Z143" t="n">
         <v>55</v>
       </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>BC Place Stadium</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>777 Pacific Boulevard, False Creek, Vancouver, British Columbia</t>
-        </is>
-      </c>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
       <c r="AC143" t="n">
         <v>1</v>
       </c>
@@ -65322,16 +64770,8 @@
       <c r="Z144" t="n">
         <v>42</v>
       </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>CenturyLink Field</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>800 Occidental Avenue South, Seattle, Washington</t>
-        </is>
-      </c>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
       <c r="AC144" t="n">
         <v>1</v>
       </c>
@@ -66622,16 +66062,8 @@
       <c r="Z147" t="n">
         <v>65</v>
       </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>Children's Mercy Park</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>One Sporting Way, Kansas City, Kansas</t>
-        </is>
-      </c>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="n">
         <v>0</v>
       </c>
@@ -67062,16 +66494,8 @@
       <c r="Z148" t="n">
         <v>47</v>
       </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>Rio Tinto Stadium</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>9256 South State Street, Sandy, Utah</t>
-        </is>
-      </c>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="n">
         <v>1</v>
       </c>
@@ -67922,16 +67346,8 @@
       <c r="Z150" t="n">
         <v>47</v>
       </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz Stadium</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>1 AMB Drive North West, Atlanta, Georgia</t>
-        </is>
-      </c>
+      <c r="AA150" t="inlineStr"/>
+      <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="n">
         <v>4</v>
       </c>
@@ -68790,16 +68206,8 @@
       <c r="Z152" t="n">
         <v>34</v>
       </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>MAPFRE Stadium</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>1 Black and Gold Boulevard, Columbus, Ohio</t>
-        </is>
-      </c>
+      <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="n">
         <v>2</v>
       </c>
@@ -69662,16 +69070,8 @@
       <c r="Z154" t="n">
         <v>45</v>
       </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>Gillette Stadium</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>1388 One Patriot Place, Foxborough, Massachusetts</t>
-        </is>
-      </c>
+      <c r="AA154" t="inlineStr"/>
+      <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="n">
         <v>3</v>
       </c>
@@ -70094,16 +69494,8 @@
       <c r="Z155" t="n">
         <v>61</v>
       </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>BBVA Compass Stadium</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>2200 Texas Avenue, East End, Houston, Texas</t>
-        </is>
-      </c>
+      <c r="AA155" t="inlineStr"/>
+      <c r="AB155" t="inlineStr"/>
       <c r="AC155" t="n">
         <v>3</v>
       </c>
@@ -73554,16 +72946,8 @@
       <c r="Z163" t="n">
         <v>47</v>
       </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>Stade Saputo</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>4750, rue Sherbrooke Est, Montreal, Quebec</t>
-        </is>
-      </c>
+      <c r="AA163" t="inlineStr"/>
+      <c r="AB163" t="inlineStr"/>
       <c r="AC163" t="n">
         <v>0</v>
       </c>
@@ -74450,16 +73834,8 @@
       <c r="Z165" t="n">
         <v>39</v>
       </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>Gillette Stadium</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>1388 One Patriot Place, Foxborough, Massachusetts</t>
-        </is>
-      </c>
+      <c r="AA165" t="inlineStr"/>
+      <c r="AB165" t="inlineStr"/>
       <c r="AC165" t="n">
         <v>0</v>
       </c>
@@ -74898,16 +74274,8 @@
       <c r="Z166" t="n">
         <v>47</v>
       </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz Stadium</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>1 AMB Drive North West, Atlanta, Georgia</t>
-        </is>
-      </c>
+      <c r="AA166" t="inlineStr"/>
+      <c r="AB166" t="inlineStr"/>
       <c r="AC166" t="n">
         <v>3</v>
       </c>
@@ -75346,16 +74714,8 @@
       <c r="Z167" t="n">
         <v>73</v>
       </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>Toyota Stadium</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>6000 Main Street, Frisco, Texas</t>
-        </is>
-      </c>
+      <c r="AA167" t="inlineStr"/>
+      <c r="AB167" t="inlineStr"/>
       <c r="AC167" t="n">
         <v>2</v>
       </c>
@@ -77086,16 +76446,8 @@
       <c r="Z171" t="n">
         <v>53</v>
       </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>CenturyLink Field</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>800 Occidental Avenue South, Seattle, Washington</t>
-        </is>
-      </c>
+      <c r="AA171" t="inlineStr"/>
+      <c r="AB171" t="inlineStr"/>
       <c r="AC171" t="n">
         <v>3</v>
       </c>
@@ -77534,16 +76886,8 @@
       <c r="Z172" t="n">
         <v>37</v>
       </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>Providence Park</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>1844 SW Morrison Street, Portland, Oregon</t>
-        </is>
-      </c>
+      <c r="AA172" t="inlineStr"/>
+      <c r="AB172" t="inlineStr"/>
       <c r="AC172" t="n">
         <v>1</v>
       </c>
@@ -77966,16 +77310,8 @@
       <c r="Z173" t="n">
         <v>58</v>
       </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>Yankee Stadium</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>One East 161st Street, The Bronx, New York City</t>
-        </is>
-      </c>
+      <c r="AA173" t="inlineStr"/>
+      <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="n">
         <v>0</v>
       </c>
@@ -78846,16 +78182,8 @@
       <c r="Z175" t="n">
         <v>33</v>
       </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>Banc of California Stadium</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>3939 S Figueroa Street, Los Angeles, California</t>
-        </is>
-      </c>
+      <c r="AA175" t="inlineStr"/>
+      <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="n">
         <v>4</v>
       </c>
@@ -79766,16 +79094,8 @@
       <c r="Z177" t="n">
         <v>48</v>
       </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>Gillette Stadium</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>1388 One Patriot Place, Foxborough, Massachusetts</t>
-        </is>
-      </c>
+      <c r="AA177" t="inlineStr"/>
+      <c r="AB177" t="inlineStr"/>
       <c r="AC177" t="n">
         <v>2</v>
       </c>
@@ -81522,16 +80842,8 @@
       <c r="Z181" t="n">
         <v>60</v>
       </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>Audi Field</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>32-60 R Street South West, Buzzard Point, Washington, District of Columbia</t>
-        </is>
-      </c>
+      <c r="AA181" t="inlineStr"/>
+      <c r="AB181" t="inlineStr"/>
       <c r="AC181" t="n">
         <v>0</v>
       </c>
@@ -81970,16 +81282,8 @@
       <c r="Z182" t="n">
         <v>57</v>
       </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>Stade Saputo</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>4750, rue Sherbrooke Est, Montreal, Quebec</t>
-        </is>
-      </c>
+      <c r="AA182" t="inlineStr"/>
+      <c r="AB182" t="inlineStr"/>
       <c r="AC182" t="n">
         <v>4</v>
       </c>
@@ -82426,16 +81730,8 @@
       <c r="Z183" t="n">
         <v>51</v>
       </c>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>Toyota Stadium</t>
-        </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>6000 Main Street, Frisco, Texas</t>
-        </is>
-      </c>
+      <c r="AA183" t="inlineStr"/>
+      <c r="AB183" t="inlineStr"/>
       <c r="AC183" t="n">
         <v>3</v>
       </c>
@@ -83718,16 +83014,8 @@
       <c r="Z186" t="n">
         <v>60</v>
       </c>
-      <c r="AA186" t="inlineStr">
-        <is>
-          <t>Children's Mercy Park</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>One Sporting Way, Kansas City, Kansas</t>
-        </is>
-      </c>
+      <c r="AA186" t="inlineStr"/>
+      <c r="AB186" t="inlineStr"/>
       <c r="AC186" t="n">
         <v>1</v>
       </c>
@@ -84146,16 +83434,8 @@
       <c r="Z187" t="n">
         <v>37</v>
       </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>CenturyLink Field</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>800 Occidental Avenue South, Seattle, Washington</t>
-        </is>
-      </c>
+      <c r="AA187" t="inlineStr"/>
+      <c r="AB187" t="inlineStr"/>
       <c r="AC187" t="n">
         <v>0</v>
       </c>
@@ -85014,16 +84294,8 @@
       <c r="Z189" t="n">
         <v>47</v>
       </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>Rio Tinto Stadium</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>9256 South State Street, Sandy, Utah</t>
-        </is>
-      </c>
+      <c r="AA189" t="inlineStr"/>
+      <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="n">
         <v>0</v>
       </c>
@@ -85462,16 +84734,8 @@
       <c r="Z190" t="n">
         <v>40</v>
       </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>Stade Saputo</t>
-        </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>4750, rue Sherbrooke Est, Montreal, Quebec</t>
-        </is>
-      </c>
+      <c r="AA190" t="inlineStr"/>
+      <c r="AB190" t="inlineStr"/>
       <c r="AC190" t="n">
         <v>4</v>
       </c>
@@ -86798,16 +86062,8 @@
       <c r="Z193" t="n">
         <v>54</v>
       </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>Gillette Stadium</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>1388 One Patriot Place, Foxborough, Massachusetts</t>
-        </is>
-      </c>
+      <c r="AA193" t="inlineStr"/>
+      <c r="AB193" t="inlineStr"/>
       <c r="AC193" t="n">
         <v>2</v>
       </c>
@@ -87254,16 +86510,8 @@
       <c r="Z194" t="n">
         <v>57</v>
       </c>
-      <c r="AA194" t="inlineStr">
-        <is>
-          <t>Audi Field</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>32-60 R Street South West, Buzzard Point, Washington, District of Columbia</t>
-        </is>
-      </c>
+      <c r="AA194" t="inlineStr"/>
+      <c r="AB194" t="inlineStr"/>
       <c r="AC194" t="n">
         <v>3</v>
       </c>
@@ -89006,16 +88254,8 @@
       <c r="Z198" t="n">
         <v>47</v>
       </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>BBVA Compass Stadium</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>2200 Texas Avenue, East End, Houston, Texas</t>
-        </is>
-      </c>
+      <c r="AA198" t="inlineStr"/>
+      <c r="AB198" t="inlineStr"/>
       <c r="AC198" t="n">
         <v>1</v>
       </c>
@@ -89438,16 +88678,8 @@
       <c r="Z199" t="n">
         <v>42</v>
       </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>CenturyLink Field</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>800 Occidental Avenue South, Seattle, Washington</t>
-        </is>
-      </c>
+      <c r="AA199" t="inlineStr"/>
+      <c r="AB199" t="inlineStr"/>
       <c r="AC199" t="n">
         <v>1</v>
       </c>
@@ -90306,16 +89538,8 @@
       <c r="Z201" t="n">
         <v>52</v>
       </c>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>Rio Tinto Stadium</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>9256 South State Street, Sandy, Utah</t>
-        </is>
-      </c>
+      <c r="AA201" t="inlineStr"/>
+      <c r="AB201" t="inlineStr"/>
       <c r="AC201" t="n">
         <v>2</v>
       </c>
@@ -92057,10 +91281,10 @@
         <v>9</v>
       </c>
       <c r="Y205" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Z205" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA205" t="inlineStr"/>
       <c r="AB205" t="inlineStr"/>
@@ -92909,10 +92133,10 @@
         <v>13</v>
       </c>
       <c r="Y207" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="Z207" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="AA207" t="inlineStr"/>
       <c r="AB207" t="inlineStr"/>
@@ -93127,10 +92351,10 @@
         <v>1</v>
       </c>
       <c r="CU207" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="CV207" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="CW207" t="n">
         <v>1</v>
@@ -93346,16 +92570,8 @@
       <c r="Z208" t="n">
         <v>56</v>
       </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>Audi Field</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>32-60 R Street South West, Buzzard Point, Washington, District of Columbia</t>
-        </is>
-      </c>
+      <c r="AA208" t="inlineStr"/>
+      <c r="AB208" t="inlineStr"/>
       <c r="AC208" t="n">
         <v>2</v>
       </c>
@@ -94646,16 +93862,8 @@
       <c r="Z211" t="n">
         <v>39</v>
       </c>
-      <c r="AA211" t="inlineStr">
-        <is>
-          <t>Children's Mercy Park</t>
-        </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>One Sporting Way, Kansas City, Kansas</t>
-        </is>
-      </c>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="inlineStr"/>
       <c r="AC211" t="n">
         <v>1</v>
       </c>
@@ -95534,16 +94742,8 @@
       <c r="Z213" t="n">
         <v>35</v>
       </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>Providence Park</t>
-        </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>1844 SW Morrison Street, Portland, Oregon</t>
-        </is>
-      </c>
+      <c r="AA213" t="inlineStr"/>
+      <c r="AB213" t="inlineStr"/>
       <c r="AC213" t="n">
         <v>1</v>
       </c>
@@ -96796,13 +95996,13 @@
         <v>2</v>
       </c>
       <c r="J216" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K216" t="n">
         <v>2</v>
       </c>
       <c r="L216" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M216" t="n">
         <v>1</v>
@@ -97294,16 +96494,8 @@
       <c r="Z217" t="n">
         <v>42</v>
       </c>
-      <c r="AA217" t="inlineStr">
-        <is>
-          <t>MAPFRE Stadium</t>
-        </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>1 Black and Gold Boulevard, Columbus, Ohio</t>
-        </is>
-      </c>
+      <c r="AA217" t="inlineStr"/>
+      <c r="AB217" t="inlineStr"/>
       <c r="AC217" t="n">
         <v>2</v>
       </c>
@@ -98174,16 +97366,8 @@
       <c r="Z219" t="n">
         <v>51</v>
       </c>
-      <c r="AA219" t="inlineStr">
-        <is>
-          <t>Banc of California Stadium</t>
-        </is>
-      </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>3939 S Figueroa Street, Los Angeles, California</t>
-        </is>
-      </c>
+      <c r="AA219" t="inlineStr"/>
+      <c r="AB219" t="inlineStr"/>
       <c r="AC219" t="n">
         <v>0</v>
       </c>
